--- a/data/cv-data/cv.xlsx
+++ b/data/cv-data/cv.xlsx
@@ -413,15 +413,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:H286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="51" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,6 +457,16 @@
           <t>group</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>org</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>program</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -477,16 +489,18 @@
           <t>Concordia University, Montreal, QC</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Concordia</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -509,16 +523,18 @@
           <t>Concordia University, Montreal, QC</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Concordia</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -541,16 +557,18 @@
           <t>Dept. of Design and Computation Arts, Faculty of Fine Arts, Concordia University</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Concordia</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -573,16 +591,18 @@
           <t>Dept. of Design and Computation Arts, Faculty of Fine Arts, Concordia University</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Concordia</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -605,16 +625,18 @@
           <t>Dept. of Design and Computation Arts, Faculty of Fine Arts, Concordia University</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Concordia</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -637,16 +659,18 @@
           <t>Dept. of Design and Computation Arts, Faculty of Fine Arts, Concordia University</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Concordia</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -669,16 +693,18 @@
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Early Career</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Arts Alliance Laboratory</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -701,16 +727,18 @@
           <t>London, England</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Early Career</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Arts Alliance Ventures</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -733,16 +761,18 @@
           <t>Palo Alto, CA</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Early Career</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Interval Research Corporation</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -765,16 +795,18 @@
           <t>San Francisco, CA</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Early Career</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fitch, Inc.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -797,16 +829,18 @@
           <t>North American Tour</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Early Career</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lollapalooza '94 Tour</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -829,16 +863,18 @@
           <t>Palo Alto, CA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Early Career</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Interval Research Corporation</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -861,16 +897,18 @@
           <t>Palo Alto, CA</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Early Career</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Institute for Research on Learning</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -893,16 +931,18 @@
           <t>Undergraduate Special Course, Stanford, CA</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Early Career</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>Employment</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -921,16 +961,14 @@
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -953,16 +991,14 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -981,16 +1017,14 @@
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1009,16 +1043,14 @@
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1037,16 +1069,14 @@
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1065,16 +1095,14 @@
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1093,16 +1121,14 @@
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1121,16 +1147,14 @@
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1149,16 +1173,14 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1177,16 +1199,14 @@
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1205,16 +1225,14 @@
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1233,16 +1251,14 @@
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1265,16 +1281,14 @@
           <t>Electronic Literature Organization</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1293,16 +1307,14 @@
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1321,16 +1333,14 @@
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1353,16 +1363,14 @@
           <t>Concordia University</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1385,16 +1393,14 @@
           <t>Electronic Literature Organization</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1413,16 +1419,14 @@
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1441,16 +1445,14 @@
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1469,16 +1471,14 @@
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1497,16 +1497,14 @@
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1525,16 +1523,14 @@
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1553,16 +1549,14 @@
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1585,16 +1579,14 @@
           <t>Digital Language, FILE Festival</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1613,16 +1605,14 @@
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1641,16 +1631,14 @@
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>Honors</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1673,16 +1661,18 @@
           <t>London, England</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Early Career</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Royal College of Art</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1705,16 +1695,18 @@
           <t>West Germany — DAAD Fellowship</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Early Career</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Freie Universität Berlin</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1737,16 +1729,18 @@
           <t>Palo Alto, CA</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Early Career</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1769,16 +1763,14 @@
           <t>Interactive installation. With E. Brechin and R. Strein. Mac OS, custom electronics, metal plinth, video projector, vellum.</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1801,16 +1793,14 @@
           <t>Interactive installation. Mac OS, custom Lingo, firehose, nozzle, projection, custom electronics.</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1833,16 +1823,14 @@
           <t>Screen interactive. Mac OS, custom Lingo.</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1865,16 +1853,14 @@
           <t>With A. Weyers. Interactive installation. Windows OS, custom C++.</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1897,16 +1883,14 @@
           <t>Screen interactive. Flash, custom Actionscript. Co-created with S. T. Fragnito.</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1929,16 +1913,14 @@
           <t>Massively multi-user public space chat system. With B. Nadeau, M. Lévesque, E. Zananiri and L. Bellemare.</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1961,16 +1943,14 @@
           <t>With B. Nadeau &amp; E. Zananiri. Interactive touchwork. Windows OS, custom Java.</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1993,16 +1973,14 @@
           <t>With Y. Assogba, D. Bouchard, and B. Nadeau. Interactive installation. Windows OS, custom Java, projection.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2025,16 +2003,14 @@
           <t>With B. Nadeau and C. Dupont. Interactive touchwork with large-scale print. Mac OS, custom Java.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2057,16 +2033,14 @@
           <t>With C. Dupont and B. Nadeau. Interactive touchwork poem for iPad/iPhone. iOS.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2089,16 +2063,14 @@
           <t>Interactive touchwork poems. With C. Gratton, S. Maheu and B. Nadeau. iOS, Objective-C.</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2121,16 +2093,14 @@
           <t>With E. Zananiri and B. Nadeau. Interactive touchwork with large-scale print. Commissioned by imagineNATIVE.</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2153,16 +2123,14 @@
           <t>With S. Maheu and B. Nadeau. Interactive touchwork poem for iPad/iPhone. iOS, Objective-C.</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2185,16 +2153,14 @@
           <t>With B. Nadeau. Interactive touchwork with large-scale print. Mac OS, custom Java.</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2217,16 +2183,14 @@
           <t>With S. Maheu and B. Nadeau. Interactive touchwork poem for iPad/iPhone. iOS, Objective-C.</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2249,16 +2213,14 @@
           <t>With B. Nadeau. Interactive touchwork with large-scale print. Mac OS, custom Java.</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>Creative Works</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2281,16 +2243,14 @@
           <t>Co-edited with Noelani Arista, Sasha Costanza-Chock, Suzanne Kite et al. Cambridge, MA: The MIT Press.</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2313,16 +2273,14 @@
           <t>Co-edited with Vivek Venkatesh, Jason Wallin, Juan Carlos Castro. Hershey: IGI Global Press.</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2345,16 +2303,14 @@
           <t>With Suzanne Kite and Scott Benesiinaabandan. All Watched Over by Machines of Loving Grace catalog, PST ART: Art &amp; Science Collide, REDCAT/CalArts, Los Angeles. In press.</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2377,16 +2333,14 @@
           <t>With Suzanne Kite and Scott Benesiinaabandan. In Syrus Marcus Ware et al. (Eds.), The Art History Book We Wish We Had: IBPOC artmaking in Northern Turtle Island. Revised and Submitted.</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2409,16 +2363,14 @@
           <t>With Ceyda Yolgörmez. In Philipp Hacker (Ed.), Oxford Intersections: AI in Society. Oxford: Oxford Academic. doi.org/10.1093/9780198945215.003.0166</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2441,16 +2393,14 @@
           <t>In Carolyn F. Strauss (Ed.), Slow Technology Reader. Amsterdam: Valiz.</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2473,16 +2423,14 @@
           <t>With Mikhel Proulx. In Karmen Cray and Joanna Hearne (Eds.), By Their Work: Indigenous Women's Digital Media in North America. University of Minnesota Press.</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2505,16 +2453,14 @@
           <t>In Amy Scott (Ed.), Future Imaginaries: Indigenous Art, Fashion, and Technology catalog, PST ART, Autry Museum of the American West, Los Angeles.</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2537,16 +2483,14 @@
           <t>With Skawennati. In Monika Kin Gagnon and Brandon Webb (Eds.), Concordia University at 50: A Collective History. Montreal: Concordia University Press.</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2569,16 +2513,14 @@
           <t>In Eleanor Drage and Kerry Mckereth (Eds.), The Good Robot: Why Technologies of the Future Need Feminism (pp. 21–27). London: Bloomsbury Press.</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2601,16 +2543,14 @@
           <t>With Noelani Arista, Archer Pechawis, and Suzanne Kite. In S. Cave, E. Drage and K. Mckereth (Eds.), Feminist AI. Oxford: Oxford University Press.</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2633,16 +2573,14 @@
           <t>In Routledge Handbook of CoFuturisms (pp. 11–22). B. Chattopadhyay et al. (Eds.). New York: Routledge. doi.org/10.4324/9780429317828</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2665,16 +2603,14 @@
           <t>In Stephen Cave and Kanta Dihal (Eds.), Imagining AI: How the World Sees Intelligent Machines (pp. 210–217). Oxford: Oxford University Press.</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2697,16 +2633,14 @@
           <t>With Michelle Lee Smith and Hémi Whaanga. In Debates in Digital Humanities 2023 (pp. 74–83). University of Minnesota Press.</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2729,16 +2663,14 @@
           <t>In Igloliorte and Taunton (Eds.), The Routledge Companion to Indigenous Art Histories in the United States and Canada (pp. 64–75).</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2761,16 +2693,14 @@
           <t>With Noelani Arista, Archer Pechawis, and Suzanne Kite. In Ben Vickers and K Allado-McDowell (Eds.), Atlas of Anomalous AI (pp. 40–51). London: Ignota Press.</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2793,16 +2723,14 @@
           <t>In Dickenson, Hill and Lalonde (Eds.), Àbadakone/Continuous Fire/Feu Continuel Exhibition Catalog (pp. 125–132). Ottawa: National Gallery of Canada.</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2825,16 +2753,14 @@
           <t>In Deanna Brown (Ed.), Other Places: Writings on Media Arts Practices in Canada (pp. 10–27). Toronto: Media Arts Network of Ontario.</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2857,16 +2783,14 @@
           <t>In Schweitzer and Henry (Eds.), Afterlives of Indigenous Archives (pp. 219–231). Lebanon: University Press of New England.</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2889,16 +2813,14 @@
           <t>In Barney et al. (Eds.), The Participatory Condition in the Digital Age (pp. 229–249). Minneapolis: University of Minnesota Press.</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2921,16 +2843,14 @@
           <t>In Steve Loft and Kerry Swanson (Eds.), Coded Territories: Tracing Indigenous Pathways in New Media (pp. 48–77). Calgary: University of Alberta Press.</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2953,16 +2873,14 @@
           <t>With Skawennati. In Pleasants and Salter (Eds.), Community-Based Multiliteracies and Digital Media Projects (pp. 111–136). New York: Peter Lang Publishing.</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2985,16 +2903,14 @@
           <t>With Elizabeth Aileen LaPensée. In Tanenbaum et al. (Eds.), Nonverbal Communications in Virtual Worlds (pp. 94–107). Pittsburgh: ETC Press.</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3017,16 +2933,14 @@
           <t>With Elizabeth Aileen LaPensée. In Jenna Ng (Ed.), Understanding Machinima (pp. 187–206). New York: Continuum Press.</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3049,16 +2963,14 @@
           <t>With Maroussia Lévesque. In Ladly and Beesley (Eds.), Mobile Nation: Creating Methodologies for Mobile Platforms (pp. 141–147). Toronto: Riverside Architectural Press.</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>Books/Chapters</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3081,16 +2993,14 @@
           <t>With Hēmi Whaanga and Ceyda Yolgörmez. AI &amp; Society. doi.org/10.1007/s00146-024-02099-4</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>Journal Articles</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3113,16 +3023,14 @@
           <t>With Noelani Arista, Archer Pechawis and Suzanne Kite. Journal of Design and Science, Issue 3.5. doi.org/10.21428/bfafd97b</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>Journal Articles</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3145,16 +3053,14 @@
           <t>With Skawennati. Leonardo 51, No. 4 (pp. 422–423).</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>Journal Articles</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3177,16 +3083,14 @@
           <t>With Skawennati. Canadian Journal of Communications, Vol. 37 No. 1.</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>Journal Articles</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3209,16 +3113,14 @@
           <t>With Beth Aileen Lameman. Journal of Game Design and Development Education, Vol. 1 No. 1.</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>Journal Articles</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3241,16 +3143,14 @@
           <t>With Bruno Nadeau. Digital Creativity vol. 21, no. 1 (pp. 18–29).</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>Journal Articles</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3273,16 +3173,14 @@
           <t>Media-Space Journal: Special Issue on Futures of New Media Art, Vol 1 no. 1.</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>Journal Articles</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3305,16 +3203,14 @@
           <t>With Yannick Assogba. Proceedings of the 14th ACM International Conference on Multimedia.</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>Journal Articles</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3337,16 +3233,14 @@
           <t>With Alex Weyers. Proceedings of UIST 1999.</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>Journal Articles</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3369,16 +3263,14 @@
           <t>Interaction 23, Zürich, Switzerland.</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3401,16 +3293,14 @@
           <t>EPIC Conference 2021. Ethnopraxis in Industry.</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3433,16 +3323,14 @@
           <t>PIVOT 2021, Pluriversal Design SIG / OCAD University, Toronto, ON.</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3465,16 +3353,14 @@
           <t>Transmediale Festival, Berlin, Germany.</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3497,16 +3383,14 @@
           <t>With Suzanne Kite. MUTEK Festival, Montreal, QC.</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3529,16 +3413,14 @@
           <t>Association of Internet Researchers (AoIR), UQAM, Montreal, QC.</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3561,16 +3443,14 @@
           <t>With Skawennati. Electronic Literature Organization Annual Conference, UQAM, Montreal, QC.</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3593,16 +3473,14 @@
           <t>Enterprising Culture Conference, CFC Media Lab, Corus Quay, Toronto, ON.</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3625,16 +3503,14 @@
           <t>Crossing Boundaries, University of Lethbridge, AB.</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3657,16 +3533,14 @@
           <t>International Visual Literacy Association Annual Conference, Concordia University, Montreal, QC.</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3689,16 +3563,14 @@
           <t>New Oceania Literary Series, University of Hawai'i at Mānoa, Honolulu, HI.</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3721,16 +3593,14 @@
           <t>TEDxMontreal 2013, Société des Arts Technologiques, Montréal, QC.</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>IIF</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>Keynotes</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3753,16 +3623,14 @@
           <t>Leonard &amp; Bina Ellen Gallery, Montreal, QC.</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>Solo Exhibitions</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3785,16 +3653,14 @@
           <t>DHC/Art &amp; the PHI Centre, Montreal, QC.</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>Solo Exhibitions</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3817,16 +3683,14 @@
           <t>Nouspace Gallery &amp; Media Lounge, Vancouver, WA.</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>Solo Exhibitions</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3849,16 +3713,14 @@
           <t>Edward Day Gallery &amp; imagineNATIVE Festival, Toronto, ON.</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>Solo Exhibitions</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3881,16 +3743,14 @@
           <t>ArtEngine, Ottawa, ON.</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>Solo Exhibitions</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3913,16 +3773,14 @@
           <t>FOFA Gallery, Montreal, QC.</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>Solo Exhibitions</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3945,16 +3803,14 @@
           <t>OBORO, Montreal, QC.</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>Solo Exhibitions</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3977,16 +3833,14 @@
           <t>Surrey Art Gallery, Surrey, B.C. Curator: Tom Konyves.</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>Group Exhibitions</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4009,16 +3863,14 @@
           <t>Biennale d'art contemporain autochtone, Montreal.</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>Group Exhibitions</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4041,16 +3893,14 @@
           <t>Stedman Gallery, Rutgers-Camden Center for the Arts, Camden NJ. Curator: Jim Brown.</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>Group Exhibitions</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4073,16 +3923,14 @@
           <t>San Jose Institute of Contemporary Art, San Jose, CA. Curator: Jody Zellen.</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>Group Exhibitions</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4105,16 +3953,14 @@
           <t>Bibliothèque Nationale Française, Paris, France.</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>Group Exhibitions</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4137,16 +3983,14 @@
           <t>Sunderland Museum and Art Gallery, Sunderland, U.K. Curator: Jeremy Theophilus.</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>Group Exhibitions</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4169,16 +4013,14 @@
           <t>Institute for Contemporary Art, Portland, ME. Curator: Linda L. Lambertson.</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>Group Exhibitions</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4201,16 +4043,14 @@
           <t>International Terminal, Pearson International Airport, Toronto, ON. Year Zero One Collective.</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>Group Exhibitions</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4233,16 +4073,14 @@
           <t>Ars Electronica Center, Linz, Austria.</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>Group Exhibitions</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4265,16 +4103,14 @@
           <t>Curators: Laurie Anderson and Brian Eno. Art Angel, Wimberley, London, England.</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Creative</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>Group Exhibitions</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4297,16 +4133,14 @@
           <t>With Skawennati. Kahnawake Survival School, Kahnawake First Nation, QC.</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4329,16 +4163,14 @@
           <t>With Skawennati. Concordia University, Montreal, QC.</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4361,16 +4193,14 @@
           <t>With Skawennati. Concordia University &amp; Kahnawake Education Centre.</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4393,16 +4223,14 @@
           <t>With Skawennati. Concordia University &amp; Kahnawake Education Centre.</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4425,16 +4253,14 @@
           <t>With Skawennati. Hālau 'Īnana, Kamehameha Schools, Honolulu, HI.</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4457,16 +4283,14 @@
           <t>With Skawennati. Hālau 'Īnana, Kamehameha Schools, Honolulu, HI.</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4489,16 +4313,14 @@
           <t>Second Life island and exhibition venue. Aboriginal Territories in Cyberspace. Producer.</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4521,16 +4343,14 @@
           <t>Video game. Unreal Engine. Montreal: Aboriginal Territories in Cyberspace. Producer.</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4553,16 +4373,14 @@
           <t>Video game. Unity 3D. Montreal: Aboriginal Territories in Cyberspace. Producer.</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4585,16 +4403,14 @@
           <t>Video game. Unity. Montreal: Aboriginal Territories in Cyberspace. Producer.</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4617,16 +4433,14 @@
           <t>Machinima series with Skawennati. Second Life. Montreal: Aboriginal Territories in Cyberspace. Executive Producer.</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4649,16 +4463,14 @@
           <t>Video game. Construct 2. Montreal: Aboriginal Territories in Cyberspace. Producer.</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4681,16 +4493,14 @@
           <t>Video game. Unity. Honolulu and Montreal: Aboriginal Territories in Cyberspace. Producer.</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4713,16 +4523,14 @@
           <t>Video game. Unity. Honolulu and Montreal: Aboriginal Territories in Cyberspace.</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4745,16 +4553,14 @@
           <t>Machinima by Skawennati. Second Life. Montreal: Aboriginal Territories in Cyberspace. Executive Producer.</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4777,16 +4583,14 @@
           <t>Film. Kanien'kehá:ka Onkwawén:na Raotitióhkwa Language and Cultural Center &amp; AbTeC. Executive Producer.</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4809,16 +4613,4918 @@
           <t>Film. Director &amp; Producer. Hawaiian International Film Festival (HIFF), Nov. 2022.</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AbTeC</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>Productions</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>11/24/2025</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>11/24/2025</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Impact Partnership Award</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>$50,000. Social Sciences and Humanities Research Council.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>04/01/2025</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>03/31/2029</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Transmediating Indigenous Art</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>$378,974. Social Sciences and Humanities Research Council.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>08/15/2024</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>An Abundant Data Trust</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>$284,000. The Schmidt Family Foundation — 11th Hour Project.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Schmidt Family Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>03/01/2023</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>02/28/2029</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Abundant Intelligences: Expanding AI through Indigenous Knowledge Systems</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>$22,830,281. New Frontiers in Research Fund.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>New Frontiers in Research Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>06/01/2023</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>05/30/2025</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Foundations of Abundant Intelligences</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>$675,000. The MacArthur Foundation.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>The MacArthur Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>04/01/2023</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>03/31/2029</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Partnership for Abundant Intelligences</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>$2,499,875. Social Sciences and Humanities Research Council.</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>04/01/2023</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>03/31/2029</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Indigenous Futures Research Centre</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>$450,609. Canada Foundation for Innovation.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Canada Foundation for Innovation</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>07/01/2023</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Abundant Intelligences Residency 1</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>$26,000. Montalvo Arts Center.</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Montalvo Arts Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>08/15/2022</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>08/14/2023</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Abundant Intelligences: Year 01</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>$98,000. The Schmidt Family Foundation — 11th Hour Project.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Schmidt Family Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>03/15/2022</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>10/30/2022</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Abundant Intelligences</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>$20,000. Social Sciences and Humanities Research Council.</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>04/01/2022</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>03/03/2024</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>L'art autochtone dans les environnements virtuels</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>$221,905. Fonds de recherche Société et culture Québec.</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Fonds de recherche du Québec</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>01/15/2022</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>01/15/2025</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Expanding Skins Workshops on Aboriginal Storytelling in Digital Media</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>$498,000. Hewitt Foundation.</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Hewitt Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>01/25/2021</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>03/30/2022</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Building Capacity with the Skins Workshops</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>$30,000. Indigenous Screen Office.</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Indigenous Screen Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>03/01/2019</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>12/31/2019</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Building Indigenous Capacity &amp; Community in Digital Media Sectors</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>$250,000. Canada Council for the Arts. Co-lead.</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Co-lead</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Canada Council for the Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>01/15/2019</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>06/01/2019</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Indigenous Protocol and Artificial Intelligence Workshops</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>$49,026. Social Sciences and Humanities Research Council.</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>09/01/2018</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>06/01/2019</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Indigenous Protocol and Artificial Intelligence Workshops</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>$80,000. Canadian Institute for Advanced Research.</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>04/01/2018</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>12/31/2018</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Skins 6.0: Kanaeokana — Workshop on Aboriginal Storytelling and Video Game Design</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>$389,000. Kanaeokana Network (Hawaii).</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Kanaeokana Network</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>04/01/2017</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>12/31/2017</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Skins 5.0: Kanaeokana — Workshop on Aboriginal Storytelling and Video Game Design</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>$187,000. Kanaeokana Network (Hawaii).</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Kanaeokana Network</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>07/01/2016</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>07/01/2017</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Blueberry Pie in the Martian Sky</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>$60,000. Canada Council for the Arts. Research Director / Executive Producer. Artist: Scott Benesiinaabandan.</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Research Director</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Canada Council for the Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>04/01/2015</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>03/31/2022</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Initiative for Indigenous Futures Partnership</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>$2,491,613. Social Sciences and Humanities Research Council.</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>06/01/2014</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>05/31/2017</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Trudeau Fellowship</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>$225,000. Pierre Elliott Trudeau Foundation.</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Fellow</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Pierre Elliott Trudeau Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>06/01/2014</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>11/03/2014</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Initiative for Indigenous Futures — Letter of Intent</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>$20,000. Social Sciences and Humanities Research Council.</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>07/01/2012</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>09/30/2013</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>The P.o.E.M.M. Cycle 6–10</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>$58,000. Canada Council for the Arts. Artist.</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Canada Council for the Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>04/01/2012</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>03/03/2015</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>TyP3: Protocoles, Plateformes, et Publics pour textes digitaux</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>$163,556. Fonds québécois de la recherche sur la société et la culture.</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Fonds québécois de la recherche</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>04/15/2012</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>04/15/2013</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Skins Workshop</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>$2,500. J. W. McConnell Family Foundation.</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>J. W. McConnell Family Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>04/01/2012</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>12/30/2013</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Abstracted Pow Wow</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>$59,000. Canada Council for the Arts. Research Director / Executive Producer. Artist: Scott Benesiinaabandan.</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Research Director</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Canada Council for the Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>04/01/2011</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>03/30/2014</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Skins, Storytellers and Second Lives: A Partnership for Developing Aboriginal New Media</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>$367,000. Social Sciences and Humanities Research Council.</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>04/01/2010</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>06/30/2011</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Words Found on an Empty Beach</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>$38,000. Canada Council for the Arts. Artist.</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Canada Council for the Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>07/01/2009</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>06/30/2010</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>TimeTraveller™</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>$60,000. Canada Council for the Arts. Research Director / Executive Producer. Artist: Skawennati Tricia Fragnito.</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Research Director</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Canada Council for the Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>07/01/2009</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>06/30/2012</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Ecriture complex: nouveaux modèles pour la typographie informatique</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>$95,000. Fonds québécois de la recherche sur la société et la culture.</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Fonds québécois de la recherche</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>04/01/2009</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>03/31/2012</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Building Aboriginal Territories in Cyberspace</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>$149,000. Fonds québécois de la recherche sur la société et la culture.</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Fonds québécois de la recherche</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>04/01/2007</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>03/31/2010</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Between Reading and Looking: Writing-Designing-Programming with Computational Media</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>$193,000. Social Sciences and Humanities Research Council.</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>04/01/2006</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>03/30/2009</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Aboriginal Territories in Cyberspace</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>$239,000. Social Sciences and Humanities Research Council.</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>06/01/2005</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>01/06/2007</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Software for Interactive, Variable and Performative Texts</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>$62,000. Hexagram Institute for Research/Creation in Media Arts and Technologies.</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Hexagram Institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>05/01/2004</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>04/30/2007</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>The Next Text</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>$39,000. Fonds québécois de la recherche sur la société et la culture.</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Fonds québécois de la recherche</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>06/01/2004</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>01/05/2005</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Writing the Next Text</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>$39,000. Hexagram Institute for Research/Creation in Media Arts and Technologies.</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Primary Investigator</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Hexagram Institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>01/15/1995</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>09/30/1995</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Life is Bait</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>$11,000. Arts Council of England. Co-grant holder.</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Co-grant Holder</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Funding (PI)</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Arts Council of England</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>04/01/2022</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>03/30/2029</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>R3AI: Shifting Paradigms for a Robust, Reasoning, &amp; Responsible AI</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>$124,000,000. Canada First Research Excellence Fund. Core Applicant. PI: Luc Vinet.</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Core Applicant</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Canada First Research Excellence Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>04/01/2022</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>03/30/2024</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Meeting 30×30 and the Paris Agreement: Leveraging Digital Solutions for Nature-Based Solutions</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>$256,623. Natural Sciences and Engineering Research Council. PI: Eliane Ubalijoro.</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Natural Sciences and Engineering Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>03/31/2022</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>03/30/2028</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Infrastructure Beyond Extractivism: Material Approaches to Restoring Indigenous Jurisdiction</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>$2,296,866. Social Sciences and Humanities Research Council. PI: Dayna Scott.</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>03/31/2021</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>03/30/2023</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Jurisdiction Back: Infrastructure beyond Extractivism</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>$246,725. New Frontiers in Research Fund. PI: Dayna Scott.</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>New Frontiers in Research Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>04/01/2020</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>03/31/2027</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Hexagram Strategic Cluster</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>$1,827,000. Fonds de recherche du Québec Société et culture. PI: Jean Dubois.</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Fonds de recherche du Québec</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>04/01/2019</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>03/31/2024</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>The Land as our Teacher: Land-based Pedagogy for/by Indigenous Youth</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>$333,000. Social Sciences and Humanities Research Council. PI: Elizabeth Fast.</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>04/01/2018</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>12/31/2025</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Inuit Futures in Arts Leadership: The Pilimmaksarniq/Pijariuqsarniq Project</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>$2,499,774. Social Sciences and Humanities Research Council. PI: Heather Igliolorte.</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>04/01/2017</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>03/23/2024</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Six Seasons of the Asiniskow Ithiniwak: Reclamation, Regeneration, and Reconciliation</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>$2,500,000. Social Sciences and Humanities Research Council. PI: Mavis Reimer.</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>04/01/2016</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>03/23/2019</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>A First Peoples Storytelling Exchange: Intersection College and Community Circles</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>$240,000. Social Sciences and Humanities Research Council. PI: Susan Briscoe.</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Social Sciences and Humanities Research Council</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>04/01/2014</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>03/03/2019</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>HexagramCIAM – Centre Interuniversitaire des Arts Médiatiques</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>$1,048,500. Fonds québécois de la recherche sur la société et la culture. PI: Christopher Salter.</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Fonds québécois de la recherche</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>04/01/2013</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>03/30/2014</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>GRAND: Graphics, Animation &amp; New Media — Collaborating Network Investigator Grant</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>$18,000. Networks of Centres of Excellence of Canada. PI: Kellogg Booth.</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>04/01/2012</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>03/30/2013</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>GRAND: Graphics, Animation &amp; New Media — Collaborating Network Investigator Grant</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>$10,000. Networks of Centres of Excellence of Canada. PI: Kellogg Booth.</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>04/01/2011</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>03/30/2014</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Hexagram CIAM</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>$367,000. Fonds Québécois de la Recherche sur la société et la culture. PIs: Nicolas Reeves, Giséle Trudel.</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>04/01/2011</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>03/30/2012</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>GRAND: Graphics, Animation &amp; New Media — Collaborating Network Investigator Grant</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>$6,000. Networks of Centres of Excellence of Canada. PI: Kellogg Booth.</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>04/01/2008</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>03/31/2011</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Migration, Memory, Media: Emergent Technologies for Interactive Narrative Storytelling</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>$119,000. Fonds québécois de la recherche sur la société et la culture. PI: Matt Soar.</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Fonds québécois de la recherche</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>04/01/2006</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>03/30/2007</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Mobile Digital Commons Network Phase II</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>$1,152,000. Heritage Canada. PIs: Michael Longford, Sara Diamond.</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Heritage Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>05/01/2004</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>04/30/2007</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Expanding the Interface</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>$135,000. Fonds québécois de la recherche sur la société et la culture. PI: Michael Longford.</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Fonds québécois de la recherche</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>08/01/2004</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>03/31/2005</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Mobile Digital Commons Network</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>$422,000. Heritage Canada. PIs: Michael Longford, Sara Diamond.</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Co-investigator</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Funding (Co-I)</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Heritage Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>06/01/2019</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>05/31/2025</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Concordia University Research Chair (Tier 1)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>$275,000. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>02/13/2019</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>10/02/2019</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Archiving Indigenous Digital Arts Conference</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>$1,800. Centre for Interdisciplinary Studies in Culture and Society, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>10/01/2019</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>10/01/2019</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Archiving Indigenous Digital Arts Conference</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>$5,965. Gail and Stephen A. Jarislowsky Institute for Studies in Canadian Art.</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Jarislowsky Institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>10/31/2017</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>08/01/2018</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Future Imaginary Lecture Series</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>$5,000. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>11/01/2016</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>10/31/2017</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Aid to Research Related Events — Future Imaginary Lecture Series</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>$5,000. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>06/01/2014</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>05/31/2019</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Concordia University Research Chair (Tier 1)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>$275,000. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>10/01/2012</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>09/30/2014</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Game Designer-in-Residency Program</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>$100,000. Office of Research, Research Development Fund.</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Concordia Office of Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>01/10/2012</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>09/30/2014</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Strategy to Frame and Strengthen Production Based Game Research</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>$50,000. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>01/11/2011</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>10/31/2012</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Vital to the General Public Welfare: An Exhibition of Research/Creation Outcomes</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>$5,000. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>10/01/2010</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>09/30/2011</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Aboriginal Territories in Cyberspace: First Contact</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>$5,000. Office of Research ARRE.</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Concordia Office of Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>03/18/2010</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>03/30/2010</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Skins Summer Institute</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>$100,000. Office of Research, Research Development Fund. Co-investigator: Skawennati Tricia Fragnito.</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Concordia Office of Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>01/01/2004</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>12/31/2011</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>SSHRC Travel Grants</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>$10,000. Fine Arts Faculty. Six separate grants.</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Concordia Fine Arts Faculty</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>04/01/2004</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>03/30/2005</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Participatory Tangible Board</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>$50,000. Fine Arts-Engineering Seed Grants.</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Concordia Fine Arts-Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>04/01/2004</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>03/30/2005</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Saying Red: Integrating Video Objects and Dynamic Typography</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>$50,000. Fine Arts-Engineering Seed Grants.</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Concordia Fine Arts-Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>01/01/2004</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Hexagram Travel Grants</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>$8,000. Fine Arts Faculty. Four separate grants.</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Funding (Internal)</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Concordia Fine Arts Faculty</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>04/30/2024</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>DART634 Indigenous Futurisms</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Graduate seminar. Concordia University, Winter 2024.</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>04/30/2023</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>DART634 Indigenous Futurisms</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Graduate seminar. Concordia University, Winter 2023.</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>04/30/2023</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>DART630 The Future Imaginary</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Graduate seminar. Concordia University, Winter 2023.</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>04/30/2022</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>DART630 The Future Imaginary</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Graduate seminar. Concordia University, Winter 2022.</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>04/30/2021</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>DART630 The Future Imaginary</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Graduate seminar. Concordia University, Winter 2021.</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>01/01/2019</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>04/30/2019</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>DART630 The Future Imaginary</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Graduate seminar. Concordia University, Winter 2019.</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>09/01/2018</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>12/31/2018</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>CART 345 Computational Texts and Typography I</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Undergraduate course. Concordia University, Fall 2018.</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>01/01/2018</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>04/30/2018</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>DART630 The Future Imaginary</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Graduate seminar. Concordia University, Winter 2018.</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>09/01/2017</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>12/31/2017</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CART 345 Computational Texts and Typography I</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Undergraduate course. Concordia University, Fall 2017.</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>09/01/2016</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>12/31/2016</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>CART 253a/b Creative Computation I</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Fall 2016.</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>09/01/2015</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>12/31/2015</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>CART 253a/b Creative Computation I</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Fall 2015.</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>09/01/2014</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>12/31/2014</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>CART 253a/b Creative Computation I</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Fall 2014.</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>01/01/2013</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>04/30/2013</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>CART 345 Computational Texts &amp; Typography I / CART 444 Portfolio Studio</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Undergraduate courses. Concordia University, Winter 2013.</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>09/01/2012</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>12/31/2012</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>CART 253a/b Creative Computation I</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Fall 2012.</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>01/01/2012</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>04/30/2012</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>CART 345 Computational Texts &amp; Typography I / CART 444 Portfolio Studio</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Undergraduate courses. Concordia University, Winter 2012.</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>09/01/2011</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>12/31/2011</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>CART 253aa/a Creative Computation I/II</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Fall 2011.</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>01/01/2011</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>04/30/2011</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>CART 253aa/a Creative Computation I/II</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Winter 2011.</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>09/01/2010</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>12/31/2010</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>CART 345 Computational Texts &amp; Typography I</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Undergraduate course. Concordia University, Fall 2010.</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>01/01/2008</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>04/30/2008</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>CART 253aa/a Creative Computation I/II</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Winter 2008.</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>09/01/2007</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>12/31/2007</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>DART 503 Theories of Interactivity / CART 355c Topics in Kinetic Imagery (The Next Text)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Graduate and undergraduate courses. Concordia University, Fall 2007.</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>01/01/2007</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>04/30/2007</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>CART 253a/b Languages of Programming</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Winter 2007.</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>09/01/2006</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>12/31/2006</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>DART 503 Theories of Interactivity / CART 355c Topics in Kinetic Imagery (The Next Text)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Graduate and undergraduate courses. Concordia University, Fall 2006.</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>04/30/2006</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>CART 253a/aa The Languages of Programming</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Winter 2006.</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>09/01/2005</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>12/31/2005</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>CART 355b Topics in Kinetic Imagery (The Next Text) / DART 503 Theories of Interactivity</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Undergraduate and graduate courses. Concordia University, Fall 2005.</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>04/30/2005</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>DFAR 253a/b The Languages of Programming</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Winter 2005.</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>01/01/2004</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>04/30/2004</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>DFAR 452 TriMedia Productions / DFAR 353a The Languages of Programming</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Undergraduate courses. Concordia University, Winter 2004.</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>09/01/2003</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>12/31/2003</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>DFAR 451 Interactive Media / DFAR 498 Bending Bits</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Undergraduate courses. Concordia University, Fall 2003.</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>04/30/2003</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>DFAR 353a/aa The Languages of Programming</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Winter 2003.</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>09/01/2002</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>12/31/2002</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>DFAR 451a/b Interactive Media</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Undergraduate course, two sections. Concordia University, Fall 2002.</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Courses Taught</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow: Melemaikalani Moniz</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow in Abundant Soils. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>12/31/2026</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow: Ceyda Yolgörmez</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Horizon Postdoctoral Fellow in Abundant Intelligences. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>01/01/2019</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>12/31/2021</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow: Leuli Eschraghi</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Horizon Postdoctoral Fellow in Indigenous Futures. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>PhD Supervisor: Juliet Mackie</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Reconstituting Indigenous Identities through Portraiture and Storytelling. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>PhD Supervisor: Mel Lefebvre</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Healing Through Ancestral Skin Marking: Traditional Tattooing as Healing and (Re)connection for Indigenous People. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>01/01/2019</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>12/31/2023</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>PhD Co-supervisor: Jessica Barudin</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Re-connecting Through Women's Teachings, Language and Movement. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>01/01/2017</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>12/31/2023</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>PhD Supervisor: Suzanne Kite</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Lakota Epistemology, Performance Practice, and Digital Technology. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>01/01/2017</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>PhD Secondary Supervisor: Nafisa Sarwath</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Indigenous knowledge, resilience and adaptive capacity. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>01/01/2016</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>12/31/2021</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>PhD Secondary Supervisor: Michelle Brown</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>(Re)Coding Resurgence: Indigenous Digital Media Kinnections. University of Hawaii Mānoa.</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>01/01/2007</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>12/31/2014</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>PhD Co-supervisor: Elizabeth LaPensée</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Simon Fraser University.</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>01/01/2008</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>12/31/2012</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>PhD Secondary Supervisor: Miao Song</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>01/01/2008</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>12/31/2011</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>PhD Secondary Supervisor: David Johnston</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Aesthetic Animism: Digital Poetry as Ontological Probe. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>PhD Committee Member: Rozita Naghshin</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Software Design as an Aesthetic Design Practice. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Masters Supervisor: Vanessa Racine</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Anishinaabe Love: Epistemologies &amp; Videogames. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>12/31/2025</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Masters Committee: Tarcisio Cataldi Tegani</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Speculative Vexillology: Exploring National Identity and Imagining Afro-Brazilian Futures through Flags. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Masters Supervisor: Caeleigh Lightning Long</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Wawêsiwîn: The Act of Dressing Up — A Research Cree-ation Project. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>01/01/2018</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>12/31/2023</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Masters Supervisor: Sébastien Aubin</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Designing Culturally Grounded Cree Syllabaries. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>01/01/2018</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>12/31/2021</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Masters Supervisor: Waylon Wilson</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Tuscarora Virtual Realities. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>01/01/2017</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>12/31/2019</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Masters Supervisor: Maize Longboat</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Haudenosaunee Storytelling via Video Games. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>01/01/2016</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>12/31/2020</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Masters Co-supervisor: Nicholas Gwyn Shulman</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Network Arts: Seeing and Making Network Organisms. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>01/01/2014</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Masters Supervisor: Morgan Kennedy</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Storied Indigeneity in Videogames: Post-Indian Warriors and Indie Japan. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>01/01/2012</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>12/31/2015</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Masters Co-supervisor: Nikolaos Chandolias</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>KinectEcho: Gesture and Vocal Recognition in New Media, Interactive Art and Live Events. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>12/31/2007</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Masters Supervisor: Leslie Plumb</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Transversal Entanglements: Research-Creation and the Design Process for Inflexions. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>01/01/2004</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Masters Co-supervisor: Mia Song</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Computer-Assisted Interactive Documentary and Performance Arts in Illimitable Space. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>12/31/2005</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Masters Committee: Rozita Naghshin</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CASE Tool Simplification Via Task-Sensitive Metaphor. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>01/01/2010</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>12/31/2018</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Acting Chair</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University. Various 1-to-2-week terms.</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>09/01/2003</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>08/31/2013</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Computation Arts Undergraduate Program Director / Co-director</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>09/01/2005</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>08/31/2008</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Graduate Program Director</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>09/01/2003</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>08/31/2014</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Computation Lab Director</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>01/01/2008</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>12/31/2020</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Personnel Committee</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>01/01/2002</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>12/31/2014</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>CART Curriculum Committee, Chair</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>01/01/2002</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Undergraduate and Graduate Admissions Committees</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Faculty Research Advisory Committee</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Faculty of Fine Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Hexagram-Concordia Steering Committee</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Co-director, Indigenous Futures Research Center</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Indigenous Directions Leadership Council</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>01/01/2015</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Milieux Research Institute Advisory Board</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>01/01/2015</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>12/31/2018</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Senate Research Committee</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>01/01/2009</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>12/31/2018</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Board Member (Founding), Research Centre on Technoculture, Art and Gaming (TAG)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>01/01/2011</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>12/31/2014</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Faculty Senate</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>12/31/2028</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Advisory Board, Digital Technologies Research Centre</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>National Research Council of Canada.</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>12/31/2023</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Advisory Council on Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Government of Canada.</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>12/31/2022</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Canadian Commission for UNESCO Working Groups on AI Ethics &amp; the Sustainable Development Goals</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>01/01/2016</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>12/31/2022</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Board Member, imagineNATIVE Film + Media Arts Festival</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>01/01/2010</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>12/31/2016</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Founding Member, New Media Advisory Board, imagineNATIVE Film + Media Arts Festival</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Co-Director, Aboriginal Territories in Cyberspace Research Network</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>01/01/2013</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>12/31/2016</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>First Peoples Literary Prize Incubating Committee &amp; Founding Advisory Board</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Blue Metropolis International Literary Festival, Montreal, QC.</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/cv-data/cv.xlsx
+++ b/data/cv-data/cv.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H286"/>
+  <dimension ref="A1:I286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -424,6 +424,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
     <col width="51" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,6 +468,11 @@
           <t>program</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>funding_group</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -501,6 +507,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -535,6 +542,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -569,6 +577,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -603,6 +612,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -637,6 +647,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -671,6 +682,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -705,6 +717,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,6 +752,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -773,6 +787,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -807,6 +822,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -841,6 +857,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -875,6 +892,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -909,6 +927,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -943,6 +962,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -969,6 +989,7 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -999,6 +1020,7 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1025,6 +1047,7 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1051,6 +1074,7 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1077,6 +1101,7 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1103,6 +1128,7 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1129,6 +1155,7 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1155,6 +1182,7 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1181,6 +1209,7 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1207,6 +1236,7 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1233,6 +1263,7 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1259,6 +1290,7 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1289,6 +1321,7 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1315,6 +1348,7 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1341,6 +1375,7 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1371,6 +1406,7 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1401,6 +1437,7 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1427,6 +1464,7 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1453,6 +1491,7 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1479,6 +1518,7 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1505,6 +1545,7 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1531,6 +1572,7 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1557,6 +1599,7 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1587,6 +1630,7 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1613,6 +1657,7 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1639,6 +1684,7 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1673,6 +1719,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1707,6 +1754,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1741,6 +1789,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1771,6 +1820,7 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1801,6 +1851,7 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1831,6 +1882,7 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1861,6 +1913,7 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1891,6 +1944,7 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1921,6 +1975,7 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1951,6 +2006,7 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1981,6 +2037,7 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2011,6 +2068,7 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2041,6 +2099,7 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2071,6 +2130,7 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2101,6 +2161,7 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2131,6 +2192,7 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2161,6 +2223,7 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2191,6 +2254,7 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2221,6 +2285,7 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2251,6 +2316,7 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2281,6 +2347,7 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2311,6 +2378,7 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2341,6 +2409,7 @@
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2371,6 +2440,7 @@
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2401,6 +2471,7 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2431,6 +2502,7 @@
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2461,6 +2533,7 @@
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2491,6 +2564,7 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2521,6 +2595,7 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2551,6 +2626,7 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2581,6 +2657,7 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2611,6 +2688,7 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2641,6 +2719,7 @@
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2671,6 +2750,7 @@
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2701,6 +2781,7 @@
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2731,6 +2812,7 @@
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2761,6 +2843,7 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2791,6 +2874,7 @@
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2821,6 +2905,7 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2851,6 +2936,7 @@
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2881,6 +2967,7 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2911,6 +2998,7 @@
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2941,6 +3029,7 @@
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2971,6 +3060,7 @@
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3001,6 +3091,7 @@
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3031,6 +3122,7 @@
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3061,6 +3153,7 @@
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3091,6 +3184,7 @@
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3121,6 +3215,7 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3151,6 +3246,7 @@
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3181,6 +3277,7 @@
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3211,6 +3308,7 @@
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3241,6 +3339,7 @@
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3271,6 +3370,7 @@
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3301,6 +3401,7 @@
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3331,6 +3432,7 @@
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3361,6 +3463,7 @@
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3391,6 +3494,7 @@
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3421,6 +3525,7 @@
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3451,6 +3556,7 @@
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3481,6 +3587,7 @@
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3511,6 +3618,7 @@
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3541,6 +3649,7 @@
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3571,6 +3680,7 @@
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3601,6 +3711,7 @@
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3631,6 +3742,7 @@
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3661,6 +3773,7 @@
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3691,6 +3804,7 @@
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3721,6 +3835,7 @@
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3751,6 +3866,7 @@
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3781,6 +3897,7 @@
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3811,6 +3928,7 @@
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3841,6 +3959,7 @@
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3871,6 +3990,7 @@
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3901,6 +4021,7 @@
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3931,6 +4052,7 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3961,6 +4083,7 @@
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3991,6 +4114,7 @@
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4021,6 +4145,7 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4051,6 +4176,7 @@
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4081,6 +4207,7 @@
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4111,6 +4238,7 @@
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4141,6 +4269,7 @@
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4171,6 +4300,7 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4201,6 +4331,7 @@
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4231,6 +4362,7 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4261,6 +4393,7 @@
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4291,6 +4424,7 @@
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4321,6 +4455,7 @@
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4351,6 +4486,7 @@
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4381,6 +4517,7 @@
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4411,6 +4548,7 @@
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4441,6 +4579,7 @@
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4471,6 +4610,7 @@
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4501,6 +4641,7 @@
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4531,6 +4672,7 @@
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4561,6 +4703,7 @@
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4591,6 +4734,7 @@
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4621,6 +4765,7 @@
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4659,6 +4804,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4697,6 +4847,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4735,6 +4890,7 @@
           <t>Schmidt Family Foundation</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4773,6 +4929,11 @@
           <t>New Frontiers in Research Fund</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4811,6 +4972,7 @@
           <t>The MacArthur Foundation</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4849,6 +5011,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4887,6 +5054,11 @@
           <t>Canada Foundation for Innovation</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4925,6 +5097,7 @@
           <t>Montalvo Arts Center</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4963,6 +5136,7 @@
           <t>Schmidt Family Foundation</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5001,6 +5175,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5039,6 +5218,7 @@
           <t>Fonds de recherche du Québec</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5077,6 +5257,7 @@
           <t>Hewitt Foundation</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5115,6 +5296,7 @@
           <t>Indigenous Screen Office</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5153,6 +5335,7 @@
           <t>Canada Council for the Arts</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5191,6 +5374,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5225,6 +5413,7 @@
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5263,6 +5452,7 @@
           <t>Kanaeokana Network</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5301,6 +5491,7 @@
           <t>Kanaeokana Network</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5339,6 +5530,7 @@
           <t>Canada Council for the Arts</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5377,6 +5569,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5415,6 +5612,7 @@
           <t>Pierre Elliott Trudeau Foundation</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5453,6 +5651,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5491,6 +5694,7 @@
           <t>Canada Council for the Arts</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5526,9 +5730,10 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Fonds québécois de la recherche</t>
-        </is>
-      </c>
+          <t>Fonds de recherche du Québec</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5567,6 +5772,7 @@
           <t>J. W. McConnell Family Foundation</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5605,6 +5811,7 @@
           <t>Canada Council for the Arts</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5643,6 +5850,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5681,6 +5893,7 @@
           <t>Canada Council for the Arts</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5719,6 +5932,7 @@
           <t>Canada Council for the Arts</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5754,9 +5968,10 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Fonds québécois de la recherche</t>
-        </is>
-      </c>
+          <t>Fonds de recherche du Québec</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5792,9 +6007,10 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Fonds québécois de la recherche</t>
-        </is>
-      </c>
+          <t>Fonds de recherche du Québec</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5833,6 +6049,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5871,6 +6092,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5909,6 +6135,7 @@
           <t>Hexagram Institute</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5944,9 +6171,10 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Fonds québécois de la recherche</t>
-        </is>
-      </c>
+          <t>Fonds de recherche du Québec</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5985,6 +6213,7 @@
           <t>Hexagram Institute</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6023,6 +6252,7 @@
           <t>Arts Council of England</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6061,6 +6291,11 @@
           <t>Canada First Research Excellence Fund</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6099,6 +6334,11 @@
           <t>Natural Sciences and Engineering Research Council</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6137,6 +6377,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6175,6 +6420,11 @@
           <t>New Frontiers in Research Fund</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6213,6 +6463,7 @@
           <t>Fonds de recherche du Québec</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6251,6 +6502,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6289,6 +6545,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6327,6 +6588,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6365,6 +6631,11 @@
           <t>Social Sciences and Humanities Research Council</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Tri-council</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6400,9 +6671,10 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Fonds québécois de la recherche</t>
-        </is>
-      </c>
+          <t>Fonds de recherche du Québec</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6437,6 +6709,7 @@
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,6 +6744,7 @@
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6505,6 +6779,7 @@
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6539,6 +6814,7 @@
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6574,9 +6850,10 @@
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Fonds québécois de la recherche</t>
-        </is>
-      </c>
+          <t>Fonds de recherche du Québec</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6615,6 +6892,7 @@
           <t>Heritage Canada</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6650,9 +6928,10 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Fonds québécois de la recherche</t>
-        </is>
-      </c>
+          <t>Fonds de recherche du Québec</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6691,6 +6970,7 @@
           <t>Heritage Canada</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6729,6 +7009,11 @@
           <t>Concordia University</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6767,6 +7052,11 @@
           <t>Concordia University</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6805,6 +7095,11 @@
           <t>Jarislowsky Institute</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6843,6 +7138,11 @@
           <t>Concordia University</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6881,6 +7181,11 @@
           <t>Concordia University</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6919,6 +7224,11 @@
           <t>Concordia University</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6954,7 +7264,12 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Concordia Office of Research</t>
+          <t>Office of Research</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Concordia</t>
         </is>
       </c>
     </row>
@@ -6995,6 +7310,11 @@
           <t>Concordia University</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7033,6 +7353,11 @@
           <t>Concordia University</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7068,7 +7393,12 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Concordia Office of Research</t>
+          <t>Office of Research</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Concordia</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7436,12 @@
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Concordia Office of Research</t>
+          <t>Office of Research</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Concordia</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7479,12 @@
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Concordia Fine Arts Faculty</t>
+          <t>Fine Arts</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Concordia</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7522,12 @@
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Concordia Fine Arts-Engineering</t>
+          <t>Fine Arts-Engineering</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Concordia</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7565,12 @@
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Concordia Fine Arts-Engineering</t>
+          <t>Fine Arts-Engineering</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Concordia</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7608,12 @@
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Concordia Fine Arts Faculty</t>
+          <t>Fine Arts</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Concordia</t>
         </is>
       </c>
     </row>
@@ -7291,6 +7646,7 @@
       </c>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7321,6 +7677,7 @@
       </c>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7351,6 +7708,7 @@
       </c>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7381,6 +7739,7 @@
       </c>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7411,6 +7770,7 @@
       </c>
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7441,6 +7801,7 @@
       </c>
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7471,6 +7832,7 @@
       </c>
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7501,6 +7863,7 @@
       </c>
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7531,6 +7894,7 @@
       </c>
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7561,6 +7925,7 @@
       </c>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7591,6 +7956,7 @@
       </c>
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7621,6 +7987,7 @@
       </c>
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7651,6 +8018,7 @@
       </c>
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7681,6 +8049,7 @@
       </c>
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7711,6 +8080,7 @@
       </c>
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7741,6 +8111,7 @@
       </c>
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7771,6 +8142,7 @@
       </c>
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7801,6 +8173,7 @@
       </c>
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7831,6 +8204,7 @@
       </c>
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7861,6 +8235,7 @@
       </c>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7891,6 +8266,7 @@
       </c>
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7921,6 +8297,7 @@
       </c>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7951,6 +8328,7 @@
       </c>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7981,6 +8359,7 @@
       </c>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8011,6 +8390,7 @@
       </c>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8041,6 +8421,7 @@
       </c>
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8071,6 +8452,7 @@
       </c>
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8101,6 +8483,7 @@
       </c>
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8131,6 +8514,7 @@
       </c>
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8161,6 +8545,7 @@
       </c>
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8191,6 +8576,7 @@
       </c>
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8221,6 +8607,7 @@
       </c>
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8251,6 +8638,7 @@
       </c>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8281,6 +8669,7 @@
       </c>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8311,6 +8700,7 @@
       </c>
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8341,6 +8731,7 @@
       </c>
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8371,6 +8762,7 @@
       </c>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8401,6 +8793,7 @@
       </c>
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8431,6 +8824,7 @@
       </c>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8461,6 +8855,7 @@
       </c>
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8491,6 +8886,7 @@
       </c>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8521,6 +8917,7 @@
       </c>
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8551,6 +8948,7 @@
       </c>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8581,6 +8979,7 @@
       </c>
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8611,6 +9010,7 @@
       </c>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8641,6 +9041,7 @@
       </c>
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8671,6 +9072,7 @@
       </c>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8701,6 +9103,7 @@
       </c>
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8731,6 +9134,7 @@
       </c>
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8761,6 +9165,7 @@
       </c>
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8791,6 +9196,7 @@
       </c>
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8821,6 +9227,7 @@
       </c>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8851,6 +9258,7 @@
       </c>
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8881,6 +9289,7 @@
       </c>
       <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8911,6 +9320,7 @@
       </c>
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8941,6 +9351,7 @@
       </c>
       <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8971,6 +9382,7 @@
       </c>
       <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9001,6 +9413,7 @@
       </c>
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9031,6 +9444,7 @@
       </c>
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9061,6 +9475,7 @@
       </c>
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9091,6 +9506,7 @@
       </c>
       <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9121,6 +9537,7 @@
       </c>
       <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9151,6 +9568,7 @@
       </c>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9181,6 +9599,7 @@
       </c>
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9211,6 +9630,7 @@
       </c>
       <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9241,6 +9661,7 @@
       </c>
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9271,6 +9692,7 @@
       </c>
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9301,6 +9723,7 @@
       </c>
       <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9331,6 +9754,7 @@
       </c>
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9361,6 +9785,7 @@
       </c>
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9391,6 +9816,7 @@
       </c>
       <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9417,6 +9843,7 @@
       </c>
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9443,6 +9870,7 @@
       </c>
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9469,6 +9897,7 @@
       </c>
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9495,6 +9924,7 @@
       </c>
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9525,6 +9955,7 @@
       </c>
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/cv-data/cv.xlsx
+++ b/data/cv-data/cv.xlsx
@@ -15457,7 +15457,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Undergraduate Honours Supervisor: [Student A]</t>
+          <t>Undergraduate [Student A] (Honours)</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Undergraduate Honours Supervisor: [Student B]</t>
+          <t>Undergraduate [Student B] (Honours)</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Undergraduate Independent Study: [Student C]</t>
+          <t>Undergraduate [Student C] (Independent Study)</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Graduate Certificate Supervisor: [Student D]</t>
+          <t>Grad Certificate [Student D]</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Graduate Certificate Supervisor: [Student E]</t>
+          <t>Grad Certificate [Student E]</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Masters Supervisor: Vanessa Racine</t>
+          <t>Masters Vanessa Racine</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Masters Committee: Tarcisio Cataldi Tegani</t>
+          <t>Masters Tarcisio Cataldi Tegani (Committee)</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Masters Supervisor: Caeleigh Lightning Long</t>
+          <t>Masters Caeleigh Lightning Long</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -15745,7 +15745,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Masters Supervisor: Sébastien Aubin</t>
+          <t>Masters Sébastien Aubin</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Masters Supervisor: Waylon Wilson</t>
+          <t>Masters Waylon Wilson</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Masters Supervisor: Maize Longboat</t>
+          <t>Masters Maize Longboat</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Masters Co-supervisor: Nicholas Gwyn Shulman</t>
+          <t>Masters Nicholas Gwyn Shulman (Co-supervisor)</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Masters Supervisor: Morgan Kennedy</t>
+          <t>Masters Morgan Kennedy</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Masters Co-supervisor: Nikolaos Chandolias</t>
+          <t>Masters Nikolaos Chandolias (Co-supervisor)</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Masters Supervisor: Leslie Plumb</t>
+          <t>Masters Leslie Plumb</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Masters Co-supervisor: Mia Song</t>
+          <t>Masters Mia Song (Co-supervisor)</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Masters Committee: Rozita Naghshin</t>
+          <t>Masters Rozita Naghshin (Committee)</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -16069,7 +16069,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>PhD Supervisor: Juliet Mackie</t>
+          <t>PhD Juliet Mackie</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -16105,7 +16105,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>PhD Supervisor: Mel Lefebvre</t>
+          <t>PhD Mel Lefebvre</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>PhD Co-supervisor: Jessica Barudin</t>
+          <t>PhD Jessica Barudin (Co-supervisor)</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>PhD Supervisor: Suzanne Kite</t>
+          <t>PhD Suzanne Kite</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>PhD Secondary Supervisor: Nafisa Sarwath</t>
+          <t>PhD Nafisa Sarwath (Secondary)</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>PhD Secondary Supervisor: Michelle Brown</t>
+          <t>PhD Michelle Brown (Secondary)</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>PhD Co-supervisor: Elizabeth LaPensée</t>
+          <t>PhD Elizabeth LaPensée (Co-supervisor)</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>PhD Secondary Supervisor: Miao Song</t>
+          <t>PhD Miao Song (Secondary)</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>PhD Secondary Supervisor: David Johnston</t>
+          <t>PhD David Johnston (Secondary)</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -16393,7 +16393,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>PhD Committee Member: Rozita Naghshin</t>
+          <t>PhD Rozita Naghshin (Committee)</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow: Melemaikalani Moniz</t>
+          <t>Postdoc Melemaikalani Moniz</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow: Ceyda Yolgörmez</t>
+          <t>Postdoc Ceyda Yolgörmez</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow: Leuli Eschraghi</t>
+          <t>Postdoc Leuli Eschraghi</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">

--- a/data/cv-data/cv.xlsx
+++ b/data/cv-data/cv.xlsx
@@ -15457,7 +15457,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Undergraduate [Student A] (Honours)</t>
+          <t>[Student A] (Honours)</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Undergraduate [Student B] (Honours)</t>
+          <t>[Student B] (Honours)</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Undergraduate [Student C] (Independent Study)</t>
+          <t>[Student C] (Independent Study)</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Grad Certificate [Student D]</t>
+          <t>[Student D]</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Grad Certificate [Student E]</t>
+          <t>[Student E]</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Masters Vanessa Racine</t>
+          <t>Vanessa Racine</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Masters Tarcisio Cataldi Tegani (Committee)</t>
+          <t>Tarcisio Cataldi Tegani (Committee)</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Masters Caeleigh Lightning Long</t>
+          <t>Caeleigh Lightning Long</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -15745,7 +15745,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Masters Sébastien Aubin</t>
+          <t>Sébastien Aubin</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Masters Waylon Wilson</t>
+          <t>Waylon Wilson</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Masters Maize Longboat</t>
+          <t>Maize Longboat</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Masters Nicholas Gwyn Shulman (Co-supervisor)</t>
+          <t>Nicholas Gwyn Shulman (Co-supervisor)</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Masters Morgan Kennedy</t>
+          <t>Morgan Kennedy</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Masters Nikolaos Chandolias (Co-supervisor)</t>
+          <t>Nikolaos Chandolias (Co-supervisor)</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Masters Leslie Plumb</t>
+          <t>Leslie Plumb</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Masters Mia Song (Co-supervisor)</t>
+          <t>Mia Song (Co-supervisor)</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Masters Rozita Naghshin (Committee)</t>
+          <t>Rozita Naghshin (Committee)</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -16069,7 +16069,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>PhD Juliet Mackie</t>
+          <t>Juliet Mackie</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -16105,7 +16105,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>PhD Mel Lefebvre</t>
+          <t>Mel Lefebvre</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>PhD Jessica Barudin (Co-supervisor)</t>
+          <t>Jessica Barudin (Co-supervisor)</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>PhD Suzanne Kite</t>
+          <t>Suzanne Kite</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>PhD Nafisa Sarwath (Secondary)</t>
+          <t>Nafisa Sarwath (Secondary)</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>PhD Michelle Brown (Secondary)</t>
+          <t>Michelle Brown (Secondary)</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>PhD Elizabeth LaPensée (Co-supervisor)</t>
+          <t>Elizabeth LaPensée (Co-supervisor)</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>PhD Miao Song (Secondary)</t>
+          <t>Miao Song (Secondary)</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>PhD David Johnston (Secondary)</t>
+          <t>David Johnston (Secondary)</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -16393,7 +16393,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>PhD Rozita Naghshin (Committee)</t>
+          <t>Rozita Naghshin (Committee)</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Postdoc Melemaikalani Moniz</t>
+          <t>Melemaikalani Moniz</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Postdoc Ceyda Yolgörmez</t>
+          <t>Ceyda Yolgörmez</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Postdoc Leuli Eschraghi</t>
+          <t>Leuli Eschraghi</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">

--- a/data/cv-data/cv.xlsx
+++ b/data/cv-data/cv.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J458"/>
+  <dimension ref="A1:J468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15555,22 +15555,22 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>[Student D]</t>
+          <t>Adriana Navarro Sainz</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>SYNTHETIC. Graduate certificate in computation arts. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
@@ -15591,22 +15591,22 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>12/31/2022</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>[Student E]</t>
+          <t>Guillaume Bourdon</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>SYNTHETIC. Graduate certificate in digital fabrication and Indigenous design. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
@@ -15627,28 +15627,28 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2013</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Vanessa Racine</t>
+          <t>Joanna Pederson</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Anishinaabe Love: Epistemologies &amp; Videogames. Concordia University.</t>
+          <t>Augmented Reality: Save the Ghost Signs. Concordia University.</t>
         </is>
       </c>
       <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G412" t="inlineStr"/>
@@ -15663,28 +15663,28 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>12/31/2025</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Tarcisio Cataldi Tegani (Committee)</t>
+          <t>Phil Lichti</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Speculative Vexillology: Exploring National Identity and Imagining Afro-Brazilian Futures through Flags. Concordia University.</t>
+          <t>The Soundwalk as Documentary Practice. Concordia University.</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G413" t="inlineStr"/>
@@ -15699,28 +15699,28 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Caeleigh Lightning Long</t>
+          <t>Santiago Salciado</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Wawêsiwîn: The Act of Dressing Up — A Research Cree-ation Project. Concordia University.</t>
+          <t>Improving the Design Process for Textbooks. Concordia University.</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G414" t="inlineStr"/>
@@ -15735,28 +15735,28 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2007</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Sébastien Aubin</t>
+          <t>Oliver Tsuji</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Designing Culturally Grounded Cree Syllabaries. Concordia University.</t>
+          <t>Narrative in Digital Media. Concordia University.</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G415" t="inlineStr"/>
@@ -15771,28 +15771,28 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>12/31/2006</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Waylon Wilson</t>
+          <t>Louis Goupille</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Tuscarora Virtual Realities. Concordia University.</t>
+          <t>Painterly Approaches to Virtual Environments. Concordia University.</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G416" t="inlineStr"/>
@@ -15807,28 +15807,28 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>12/31/2019</t>
+          <t>12/31/2006</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Maize Longboat</t>
+          <t>Thibaut Duverneix</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Haudenosaunee Storytelling via Video Games. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G417" t="inlineStr"/>
@@ -15843,28 +15843,28 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>12/31/2020</t>
+          <t>12/31/2004</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Nicholas Gwyn Shulman (Co-supervisor)</t>
+          <t>Farah Jamaluddin</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Network Arts: Seeing and Making Network Organisms. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G418" t="inlineStr"/>
@@ -15879,28 +15879,28 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2005</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Morgan Kennedy</t>
+          <t>Dalia Radwan</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Storied Indigeneity in Videogames: Post-Indian Warriors and Indie Japan. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G419" t="inlineStr"/>
@@ -15915,28 +15915,28 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2002</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>12/31/2003</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Nikolaos Chandolias (Co-supervisor)</t>
+          <t>John Stuart</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>KinectEcho: Gesture and Vocal Recognition in New Media, Interactive Art and Live Events. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G420" t="inlineStr"/>
@@ -15951,28 +15951,28 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2002</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>12/31/2007</t>
+          <t>12/31/2003</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Leslie Plumb</t>
+          <t>Justyna Latek</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Transversal Entanglements: Research-Creation and the Design Process for Inflexions. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G421" t="inlineStr"/>
@@ -15987,22 +15987,22 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>01/01/2004</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Mia Song (Co-supervisor)</t>
+          <t>Vanessa Racine</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Computer-Assisted Interactive Documentary and Performance Arts in Illimitable Space. Concordia University.</t>
+          <t>Anishinaabe Love: Epistemologies &amp; Videogames. Concordia University.</t>
         </is>
       </c>
       <c r="E422" t="inlineStr"/>
@@ -16023,22 +16023,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>12/31/2005</t>
+          <t>12/31/2025</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Rozita Naghshin (Committee)</t>
+          <t>Tarcisio Cataldi Tegani (Committee)</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>CASE Tool Simplification Via Task-Sensitive Metaphor. Concordia University.</t>
+          <t>Speculative Vexillology: Exploring National Identity and Imagining Afro-Brazilian Futures through Flags. Concordia University.</t>
         </is>
       </c>
       <c r="E423" t="inlineStr"/>
@@ -16059,28 +16059,28 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Juliet Mackie</t>
+          <t>Caeleigh Lightning Long</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Reconstituting Indigenous Identities through Portraiture and Storytelling. Concordia University.</t>
+          <t>Wawêsiwîn: The Act of Dressing Up — A Research Cree-ation Project. Concordia University.</t>
         </is>
       </c>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G424" t="inlineStr"/>
@@ -16095,28 +16095,28 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2023</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Mel Lefebvre</t>
+          <t>Sébastien Aubin</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Healing Through Ancestral Skin Marking: Traditional Tattooing as Healing and (Re)connection for Indigenous People. Concordia University.</t>
+          <t>Designing Culturally Grounded Cree Syllabaries. Concordia University.</t>
         </is>
       </c>
       <c r="E425" t="inlineStr"/>
       <c r="F425" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G425" t="inlineStr"/>
@@ -16131,28 +16131,28 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Jessica Barudin (Co-supervisor)</t>
+          <t>Waylon Wilson</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Re-connecting Through Women's Teachings, Language and Movement. Concordia University.</t>
+          <t>Tuscarora Virtual Realities. Concordia University.</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G426" t="inlineStr"/>
@@ -16172,23 +16172,23 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2019</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Suzanne Kite</t>
+          <t>Maize Longboat</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Lakota Epistemology, Performance Practice, and Digital Technology. Concordia University.</t>
+          <t>Haudenosaunee Storytelling via Video Games. Concordia University.</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G427" t="inlineStr"/>
@@ -16203,28 +16203,28 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2020</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Nafisa Sarwath (Secondary)</t>
+          <t>Nicholas Gwyn Shulman (Co-supervisor)</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Indigenous knowledge, resilience and adaptive capacity. Concordia University.</t>
+          <t>Network Arts: Seeing and Making Network Organisms. Concordia University.</t>
         </is>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G428" t="inlineStr"/>
@@ -16239,28 +16239,28 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Michelle Brown (Secondary)</t>
+          <t>Morgan Kennedy</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>(Re)Coding Resurgence: Indigenous Digital Media Kinnections. University of Hawaii Mānoa.</t>
+          <t>Storied Indigeneity in Videogames: Post-Indian Warriors and Indie Japan. Concordia University.</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G429" t="inlineStr"/>
@@ -16275,28 +16275,28 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>12/31/2014</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Elizabeth LaPensée (Co-supervisor)</t>
+          <t>Nikolaos Chandolias (Co-supervisor)</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Simon Fraser University.</t>
+          <t>KinectEcho: Gesture and Vocal Recognition in New Media, Interactive Art and Live Events. Concordia University.</t>
         </is>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G430" t="inlineStr"/>
@@ -16311,28 +16311,28 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>01/01/2008</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>12/31/2012</t>
+          <t>12/31/2007</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Miao Song (Secondary)</t>
+          <t>Leslie Plumb</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Concordia University.</t>
+          <t>Transversal Entanglements: Research-Creation and the Design Process for Inflexions. Concordia University.</t>
         </is>
       </c>
       <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G431" t="inlineStr"/>
@@ -16347,28 +16347,28 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>01/01/2008</t>
+          <t>01/01/2004</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2008</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>David Johnston (Secondary)</t>
+          <t>Mia Song (Co-supervisor)</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Aesthetic Animism: Digital Poetry as Ontological Probe. Concordia University.</t>
+          <t>Computer-Assisted Interactive Documentary and Performance Arts in Illimitable Space. Concordia University.</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G432" t="inlineStr"/>
@@ -16383,12 +16383,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>12/31/2005</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -16398,13 +16398,13 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Software Design as an Aesthetic Design Practice. Concordia University.</t>
+          <t>CASE Tool Simplification Via Task-Sensitive Metaphor. Concordia University.</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
       <c r="F433" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G433" t="inlineStr"/>
@@ -16419,7 +16419,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16429,18 +16429,18 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Melemaikalani Moniz</t>
+          <t>Juliet Mackie</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow in Abundant Soils. Concordia University.</t>
+          <t>Reconstituting Indigenous Identities through Portraiture and Storytelling. Concordia University.</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G434" t="inlineStr"/>
@@ -16455,28 +16455,28 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>12/31/2026</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Ceyda Yolgörmez</t>
+          <t>Mel Lefebvre</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Horizon Postdoctoral Fellow in Abundant Intelligences. Concordia University.</t>
+          <t>Healing Through Ancestral Skin Marking: Traditional Tattooing as Healing and (Re)connection for Indigenous People. Concordia University.</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G435" t="inlineStr"/>
@@ -16496,23 +16496,23 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>12/31/2023</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Leuli Eschraghi</t>
+          <t>Jessica Barudin (Co-supervisor)</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Horizon Postdoctoral Fellow in Indigenous Futures. Concordia University.</t>
+          <t>Re-connecting Through Women's Teachings, Language and Movement. Concordia University.</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G436" t="inlineStr"/>
@@ -16527,130 +16527,146 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2023</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Acting Chair</t>
+          <t>Suzanne Kite</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University. Various 1-to-2-week terms.</t>
+          <t>Lakota Epistemology, Performance Practice, and Digital Technology. Concordia University.</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr"/>
       <c r="I437" t="inlineStr"/>
-      <c r="J437" t="inlineStr"/>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>09/01/2003</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>08/31/2013</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Computation Arts Undergraduate Program Director / Co-director</t>
+          <t>Nafisa Sarwath (Secondary)</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>Indigenous knowledge, resilience and adaptive capacity. Concordia University.</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr"/>
       <c r="I438" t="inlineStr"/>
-      <c r="J438" t="inlineStr"/>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>09/01/2005</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>08/31/2008</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Graduate Program Director</t>
+          <t>Michelle Brown (Secondary)</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>(Re)Coding Resurgence: Indigenous Digital Media Kinnections. University of Hawaii Mānoa.</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr"/>
       <c r="I439" t="inlineStr"/>
-      <c r="J439" t="inlineStr"/>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>09/01/2003</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>08/31/2014</t>
+          <t>12/31/2014</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Computation Lab Director</t>
+          <t>Elizabeth LaPensée (Co-supervisor)</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Simon Fraser University.</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr"/>
-      <c r="J440" t="inlineStr"/>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -16660,209 +16676,233 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>12/31/2020</t>
+          <t>12/31/2012</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Personnel Committee</t>
+          <t>Miao Song (Secondary)</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Concordia University.</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr"/>
       <c r="I441" t="inlineStr"/>
-      <c r="J441" t="inlineStr"/>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>01/01/2002</t>
+          <t>01/01/2008</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>12/31/2014</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>CART Curriculum Committee, Chair</t>
+          <t>David Johnston (Secondary)</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>Aesthetic Animism: Digital Poetry as Ontological Probe. Concordia University.</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr"/>
-      <c r="J442" t="inlineStr"/>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>01/01/2002</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2008</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Undergraduate and Graduate Admissions Committees</t>
+          <t>Rozita Naghshin (Committee)</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>Software Design as an Aesthetic Design Practice. Concordia University.</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr"/>
-      <c r="J443" t="inlineStr"/>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Faculty Research Advisory Committee</t>
+          <t>Melemaikalani Moniz</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Faculty of Fine Arts, Concordia University.</t>
+          <t>Postdoctoral Fellow in Abundant Soils. Concordia University.</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Postdoc</t>
         </is>
       </c>
       <c r="G444" t="inlineStr"/>
       <c r="H444" t="inlineStr"/>
       <c r="I444" t="inlineStr"/>
-      <c r="J444" t="inlineStr"/>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>12/31/2026</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Hexagram-Concordia Steering Committee</t>
+          <t>Ceyda Yolgörmez</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Horizon Postdoctoral Fellow in Abundant Intelligences. Concordia University.</t>
         </is>
       </c>
       <c r="E445" t="inlineStr"/>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Postdoc</t>
         </is>
       </c>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr"/>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Co-director, Indigenous Futures Research Center</t>
+          <t>Leuli Eschraghi</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Horizon Postdoctoral Fellow in Indigenous Futures. Concordia University.</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Postdoc</t>
         </is>
       </c>
       <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr"/>
       <c r="I446" t="inlineStr"/>
-      <c r="J446" t="inlineStr"/>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Indigenous Directions Leadership Council</t>
+          <t>Acting Chair</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Department of Design and Computation Arts, Concordia University. Various 1-to-2-week terms.</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
@@ -16879,22 +16919,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>09/01/2003</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>08/31/2013</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Milieux Research Institute Advisory Board</t>
+          <t>Computation Arts Undergraduate Program Director / Co-director</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
@@ -16911,22 +16951,22 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>09/01/2005</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>08/31/2008</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Senate Research Committee</t>
+          <t>Graduate Program Director</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
@@ -16943,22 +16983,22 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>01/01/2009</t>
+          <t>09/01/2003</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>08/31/2014</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Board Member (Founding), Research Centre on Technoculture, Art and Gaming (TAG)</t>
+          <t>Computation Lab Director</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -16975,22 +17015,22 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>01/01/2008</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>12/31/2014</t>
+          <t>12/31/2020</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Faculty Senate</t>
+          <t>Personnel Committee</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
@@ -17007,22 +17047,22 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2002</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>12/31/2028</t>
+          <t>12/31/2014</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Advisory Board, Digital Technologies Research Centre</t>
+          <t>CART Curriculum Committee, Chair</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>National Research Council of Canada.</t>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
         </is>
       </c>
       <c r="E452" t="inlineStr"/>
@@ -17039,22 +17079,22 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2002</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Advisory Council on Artificial Intelligence</t>
+          <t>Undergraduate and Graduate Admissions Committees</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Government of Canada.</t>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
@@ -17071,20 +17111,24 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>12/31/2022</t>
+          <t>12/31/2008</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Canadian Commission for UNESCO Working Groups on AI Ethics &amp; the Sustainable Development Goals</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr"/>
+          <t>Faculty Research Advisory Committee</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Faculty of Fine Arts, Concordia University.</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr">
         <is>
@@ -17099,20 +17143,24 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>12/31/2022</t>
+          <t>12/31/2008</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Board Member, imagineNATIVE Film + Media Arts Festival</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr"/>
+          <t>Hexagram-Concordia Steering Committee</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr">
         <is>
@@ -17127,20 +17175,24 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>12/31/2016</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Founding Member, New Media Advisory Board, imagineNATIVE Film + Media Arts Festival</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr"/>
+          <t>Co-director, Indigenous Futures Research Center</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr"/>
       <c r="F456" t="inlineStr">
         <is>
@@ -17155,7 +17207,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -17165,10 +17217,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Co-Director, Aboriginal Territories in Cyberspace Research Network</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr"/>
+          <t>Indigenous Directions Leadership Council</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr">
         <is>
@@ -17183,22 +17239,22 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>01/01/2013</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>12/31/2016</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>First Peoples Literary Prize Incubating Committee &amp; Founding Advisory Board</t>
+          <t>Milieux Research Institute Advisory Board</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Blue Metropolis International Literary Festival, Montreal, QC.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -17212,6 +17268,310 @@
       <c r="I458" t="inlineStr"/>
       <c r="J458" t="inlineStr"/>
     </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>01/01/2015</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>12/31/2018</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Senate Research Committee</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr"/>
+      <c r="J459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>01/01/2009</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>12/31/2018</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Board Member (Founding), Research Centre on Technoculture, Art and Gaming (TAG)</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr"/>
+      <c r="I460" t="inlineStr"/>
+      <c r="J460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>01/01/2011</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>12/31/2014</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Faculty Senate</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>12/31/2028</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Advisory Board, Digital Technologies Research Centre</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>National Research Council of Canada.</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr"/>
+      <c r="J462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>12/31/2023</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Advisory Council on Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Government of Canada.</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr"/>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+      <c r="J463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>12/31/2022</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Canadian Commission for UNESCO Working Groups on AI Ethics &amp; the Sustainable Development Goals</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr"/>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>01/01/2016</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>12/31/2022</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Board Member, imagineNATIVE Film + Media Arts Festival</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
+      <c r="E465" t="inlineStr"/>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>01/01/2010</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>12/31/2016</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Founding Member, New Media Advisory Board, imagineNATIVE Film + Media Arts Festival</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr"/>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr"/>
+      <c r="J466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Co-Director, Aboriginal Territories in Cyberspace Research Network</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>01/01/2013</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>12/31/2016</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>First Peoples Literary Prize Incubating Committee &amp; Founding Advisory Board</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Blue Metropolis International Literary Festival, Montreal, QC.</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr"/>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr"/>
+      <c r="J468" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cv-data/cv.xlsx
+++ b/data/cv-data/cv.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J468"/>
+  <dimension ref="A1:J551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>[Student A] (Honours)</t>
+          <t>Destiny Chescappio</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>SYNTHETIC. Honours thesis in computation arts and Indigenous futures. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E407" t="inlineStr"/>
@@ -15483,22 +15483,22 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>[Student B] (Honours)</t>
+          <t>Hazel Dreslinski</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>SYNTHETIC. Independent study in interactive media and land-based knowledge. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E408" t="inlineStr"/>
@@ -15519,22 +15519,22 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>12/31/2020</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>[Student C] (Independent Study)</t>
+          <t>Margaret Summers</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>SYNTHETIC. Creative coding and Indigenous language revitalization. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E409" t="inlineStr"/>
@@ -15555,28 +15555,28 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Adriana Navarro Sainz</t>
+          <t>Milo Puge</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G410" t="inlineStr"/>
@@ -15591,28 +15591,28 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>12/31/2025</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Guillaume Bourdon</t>
+          <t>Jerwin Cabaneros</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G411" t="inlineStr"/>
@@ -15627,28 +15627,28 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>12/31/2013</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Joanna Pederson</t>
+          <t>Taylor McArthur</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Augmented Reality: Save the Ghost Signs. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G412" t="inlineStr"/>
@@ -15663,28 +15663,28 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Phil Lichti</t>
+          <t>Sarah Hontoy-Major</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>The Soundwalk as Documentary Practice. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G413" t="inlineStr"/>
@@ -15699,28 +15699,28 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Santiago Salciado</t>
+          <t>Neko Wong-Houle</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Improving the Design Process for Textbooks. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G414" t="inlineStr"/>
@@ -15735,28 +15735,28 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>12/31/2007</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Oliver Tsuji</t>
+          <t>Ixel Janine</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Narrative in Digital Media. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G415" t="inlineStr"/>
@@ -15771,28 +15771,28 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>12/31/2006</t>
+          <t>12/31/2023</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Louis Goupille</t>
+          <t>Wan Hua (Wawa) Li</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Painterly Approaches to Virtual Environments. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G416" t="inlineStr"/>
@@ -15807,28 +15807,28 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>12/31/2006</t>
+          <t>12/31/2023</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Thibaut Duverneix</t>
+          <t>Bronson Jacque</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G417" t="inlineStr"/>
@@ -15843,28 +15843,28 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>12/31/2004</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Farah Jamaluddin</t>
+          <t>Shirley Ceravolo</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G418" t="inlineStr"/>
@@ -15879,28 +15879,28 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>12/31/2005</t>
+          <t>12/31/2022</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Dalia Radwan</t>
+          <t>Alanna Mitchell</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G419" t="inlineStr"/>
@@ -15915,28 +15915,28 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>01/01/2002</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>12/31/2003</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>John Stuart</t>
+          <t>Anthony Lum</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G420" t="inlineStr"/>
@@ -15951,28 +15951,28 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>01/01/2002</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>12/31/2003</t>
+          <t>12/31/2022</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Justyna Latek</t>
+          <t>Unna Regino</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G421" t="inlineStr"/>
@@ -15987,28 +15987,28 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2019</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Vanessa Racine</t>
+          <t>Alaina Perez</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Anishinaabe Love: Epistemologies &amp; Videogames. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G422" t="inlineStr"/>
@@ -16023,28 +16023,28 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>12/31/2025</t>
+          <t>12/31/2020</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Tarcisio Cataldi Tegani (Committee)</t>
+          <t>Kahentawaks Tiewishaw</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Speculative Vexillology: Exploring National Identity and Imagining Afro-Brazilian Futures through Flags. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G423" t="inlineStr"/>
@@ -16059,28 +16059,28 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2019</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Caeleigh Lightning Long</t>
+          <t>Lucas LaRochelle</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Wawêsiwîn: The Act of Dressing Up — A Research Cree-ation Project. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G424" t="inlineStr"/>
@@ -16095,28 +16095,28 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2019</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Sébastien Aubin</t>
+          <t>Samuelle Bourgault</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Designing Culturally Grounded Cree Syllabaries. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E425" t="inlineStr"/>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G425" t="inlineStr"/>
@@ -16131,28 +16131,28 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Waylon Wilson</t>
+          <t>Alexandria Alcancia-Shaw</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Tuscarora Virtual Realities. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G426" t="inlineStr"/>
@@ -16172,23 +16172,23 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>12/31/2019</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Maize Longboat</t>
+          <t>Asa Perlman</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Haudenosaunee Storytelling via Video Games. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G427" t="inlineStr"/>
@@ -16203,28 +16203,28 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>12/31/2020</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Nicholas Gwyn Shulman (Co-supervisor)</t>
+          <t>Dion Smith-Dokkie</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Network Arts: Seeing and Making Network Organisms. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G428" t="inlineStr"/>
@@ -16239,28 +16239,28 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Morgan Kennedy</t>
+          <t>Eileen Peng</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Storied Indigeneity in Videogames: Post-Indian Warriors and Indie Japan. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G429" t="inlineStr"/>
@@ -16275,28 +16275,28 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Nikolaos Chandolias (Co-supervisor)</t>
+          <t>Rudi Aker</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>KinectEcho: Gesture and Vocal Recognition in New Media, Interactive Art and Live Events. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G430" t="inlineStr"/>
@@ -16311,28 +16311,28 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>12/31/2007</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Leslie Plumb</t>
+          <t>Sarah Lauzon</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Transversal Entanglements: Research-Creation and the Design Process for Inflexions. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G431" t="inlineStr"/>
@@ -16347,28 +16347,28 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>01/01/2004</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Mia Song (Co-supervisor)</t>
+          <t>Simon-Albert Boudreault</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Computer-Assisted Interactive Documentary and Performance Arts in Illimitable Space. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G432" t="inlineStr"/>
@@ -16383,28 +16383,28 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>12/31/2005</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Rozita Naghshin (Committee)</t>
+          <t>Victor Ivanov</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>CASE Tool Simplification Via Task-Sensitive Metaphor. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G433" t="inlineStr"/>
@@ -16419,28 +16419,28 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2020</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Juliet Mackie</t>
+          <t>Emmanuelle Forgues</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Reconstituting Indigenous Identities through Portraiture and Storytelling. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G434" t="inlineStr"/>
@@ -16455,28 +16455,28 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Mel Lefebvre</t>
+          <t>Roxanne Sirois</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Healing Through Ancestral Skin Marking: Traditional Tattooing as Healing and (Re)connection for Indigenous People. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
       <c r="F435" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G435" t="inlineStr"/>
@@ -16491,28 +16491,28 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Jessica Barudin (Co-supervisor)</t>
+          <t>Darian Jacobs</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Re-connecting Through Women's Teachings, Language and Movement. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
       <c r="F436" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G436" t="inlineStr"/>
@@ -16527,28 +16527,28 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2019</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Suzanne Kite</t>
+          <t>Travis Mercredi</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Lakota Epistemology, Performance Practice, and Digital Technology. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G437" t="inlineStr"/>
@@ -16563,28 +16563,28 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Nafisa Sarwath (Secondary)</t>
+          <t>David Clark</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Indigenous knowledge, resilience and adaptive capacity. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G438" t="inlineStr"/>
@@ -16599,28 +16599,28 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Michelle Brown (Secondary)</t>
+          <t>Christina Biron</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>(Re)Coding Resurgence: Indigenous Digital Media Kinnections. University of Hawaii Mānoa.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G439" t="inlineStr"/>
@@ -16635,28 +16635,28 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>12/31/2014</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Elizabeth LaPensée (Co-supervisor)</t>
+          <t>Nicole Linn</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Simon Fraser University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G440" t="inlineStr"/>
@@ -16671,28 +16671,28 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>01/01/2008</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>12/31/2012</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Miao Song (Secondary)</t>
+          <t>Mi Lin Li</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G441" t="inlineStr"/>
@@ -16707,28 +16707,28 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>01/01/2008</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>David Johnston (Secondary)</t>
+          <t>Lianne Maritzer</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Aesthetic Animism: Digital Poetry as Ontological Probe. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G442" t="inlineStr"/>
@@ -16743,28 +16743,28 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Rozita Naghshin (Committee)</t>
+          <t>Julian Glass-Pilon</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Software Design as an Aesthetic Design Practice. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G443" t="inlineStr"/>
@@ -16779,28 +16779,28 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Melemaikalani Moniz</t>
+          <t>Erica Perrault</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow in Abundant Soils. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G444" t="inlineStr"/>
@@ -16815,28 +16815,28 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>12/31/2026</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Ceyda Yolgörmez</t>
+          <t>Charles Hannah</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Horizon Postdoctoral Fellow in Abundant Intelligences. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E445" t="inlineStr"/>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G445" t="inlineStr"/>
@@ -16851,28 +16851,28 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Leuli Eschraghi</t>
+          <t>Nather Aylomen</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Horizon Postdoctoral Fellow in Indigenous Futures. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G446" t="inlineStr"/>
@@ -16887,690 +16887,3678 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2013</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Acting Chair</t>
+          <t>Näiade Aoun</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University. Various 1-to-2-week terms.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr"/>
       <c r="I447" t="inlineStr"/>
-      <c r="J447" t="inlineStr"/>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>09/01/2003</t>
+          <t>01/01/2013</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>08/31/2013</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Computation Arts Undergraduate Program Director / Co-director</t>
+          <t>Alicia McDonald-Fortier</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
       <c r="I448" t="inlineStr"/>
-      <c r="J448" t="inlineStr"/>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>09/01/2005</t>
+          <t>01/01/2013</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>08/31/2008</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Graduate Program Director</t>
+          <t>Serge Maheau</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr"/>
-      <c r="J449" t="inlineStr"/>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>09/01/2003</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>08/31/2014</t>
+          <t>12/31/2014</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Computation Lab Director</t>
+          <t>David Mongeau-Petitepas</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr"/>
       <c r="I450" t="inlineStr"/>
-      <c r="J450" t="inlineStr"/>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>01/01/2008</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>12/31/2020</t>
+          <t>12/31/2014</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Personnel Committee</t>
+          <t>Saurabh Oberoi</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr"/>
       <c r="I451" t="inlineStr"/>
-      <c r="J451" t="inlineStr"/>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>01/01/2002</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>12/31/2014</t>
+          <t>12/31/2013</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>CART Curriculum Committee, Chair</t>
+          <t>Andy Lunga</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr"/>
-      <c r="J452" t="inlineStr"/>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>01/01/2002</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2012</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Undergraduate and Graduate Admissions Committees</t>
+          <t>Bronson Zgeb</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Department of Design and Computation Arts, Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G453" t="inlineStr"/>
       <c r="H453" t="inlineStr"/>
       <c r="I453" t="inlineStr"/>
-      <c r="J453" t="inlineStr"/>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>12/31/2012</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Faculty Research Advisory Committee</t>
+          <t>Megan Whyte</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Faculty of Fine Arts, Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr"/>
       <c r="I454" t="inlineStr"/>
-      <c r="J454" t="inlineStr"/>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Hexagram-Concordia Steering Committee</t>
+          <t>Laura Sirois</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr"/>
       <c r="I455" t="inlineStr"/>
-      <c r="J455" t="inlineStr"/>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Co-director, Indigenous Futures Research Center</t>
+          <t>Robert Brais</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E456" t="inlineStr"/>
       <c r="F456" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr"/>
       <c r="I456" t="inlineStr"/>
-      <c r="J456" t="inlineStr"/>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Indigenous Directions Leadership Council</t>
+          <t>Marie-Joelle Gringas</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G457" t="inlineStr"/>
       <c r="H457" t="inlineStr"/>
       <c r="I457" t="inlineStr"/>
-      <c r="J457" t="inlineStr"/>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Milieux Research Institute Advisory Board</t>
+          <t>Natalie Pan</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G458" t="inlineStr"/>
       <c r="H458" t="inlineStr"/>
       <c r="I458" t="inlineStr"/>
-      <c r="J458" t="inlineStr"/>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Senate Research Committee</t>
+          <t>Chris Drogaris</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G459" t="inlineStr"/>
       <c r="H459" t="inlineStr"/>
       <c r="I459" t="inlineStr"/>
-      <c r="J459" t="inlineStr"/>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>01/01/2009</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Board Member (Founding), Research Centre on Technoculture, Art and Gaming (TAG)</t>
+          <t>Tania Alvarez</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G460" t="inlineStr"/>
       <c r="H460" t="inlineStr"/>
       <c r="I460" t="inlineStr"/>
-      <c r="J460" t="inlineStr"/>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>12/31/2014</t>
+          <t>12/31/2010</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Faculty Senate</t>
+          <t>Chris Gratton</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G461" t="inlineStr"/>
       <c r="H461" t="inlineStr"/>
       <c r="I461" t="inlineStr"/>
-      <c r="J461" t="inlineStr"/>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>12/31/2028</t>
+          <t>12/31/2010</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Advisory Board, Digital Technologies Research Centre</t>
+          <t>Brian Li</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>National Research Council of Canada.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G462" t="inlineStr"/>
       <c r="H462" t="inlineStr"/>
       <c r="I462" t="inlineStr"/>
-      <c r="J462" t="inlineStr"/>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2010</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Advisory Council on Artificial Intelligence</t>
+          <t>Charles-Antoine Dupont</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Government of Canada.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G463" t="inlineStr"/>
       <c r="H463" t="inlineStr"/>
       <c r="I463" t="inlineStr"/>
-      <c r="J463" t="inlineStr"/>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>12/31/2022</t>
+          <t>12/31/2010</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Canadian Commission for UNESCO Working Groups on AI Ethics &amp; the Sustainable Development Goals</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr"/>
+          <t>Ramy Daghistani</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G464" t="inlineStr"/>
       <c r="H464" t="inlineStr"/>
       <c r="I464" t="inlineStr"/>
-      <c r="J464" t="inlineStr"/>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2009</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>12/31/2022</t>
+          <t>12/31/2013</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Board Member, imagineNATIVE Film + Media Arts Festival</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr"/>
+          <t>Charlotte Fischer</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G465" t="inlineStr"/>
       <c r="H465" t="inlineStr"/>
       <c r="I465" t="inlineStr"/>
-      <c r="J465" t="inlineStr"/>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2009</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>12/31/2016</t>
+          <t>12/31/2013</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Founding Member, New Media Advisory Board, imagineNATIVE Film + Media Arts Festival</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr"/>
+          <t>Sahar Homami</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G466" t="inlineStr"/>
       <c r="H466" t="inlineStr"/>
       <c r="I466" t="inlineStr"/>
-      <c r="J466" t="inlineStr"/>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2013</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Co-Director, Aboriginal Territories in Cyberspace Research Network</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr"/>
+          <t>Nancy Elizabeth-Townsend</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr"/>
       <c r="F467" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G467" t="inlineStr"/>
       <c r="H467" t="inlineStr"/>
       <c r="I467" t="inlineStr"/>
-      <c r="J467" t="inlineStr"/>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>01/01/2013</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>12/31/2016</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>First Peoples Literary Prize Incubating Committee &amp; Founding Advisory Board</t>
+          <t>Mohannad Al-Khatib</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Blue Metropolis International Literary Festival, Montreal, QC.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E468" t="inlineStr"/>
       <c r="F468" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G468" t="inlineStr"/>
       <c r="H468" t="inlineStr"/>
       <c r="I468" t="inlineStr"/>
-      <c r="J468" t="inlineStr"/>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>01/01/2007</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>12/31/2009</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Cassandra Lacombe</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr"/>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr"/>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>01/01/2007</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>12/31/2009</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Raed Mousa</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr"/>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr"/>
+      <c r="I470" t="inlineStr"/>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>01/01/2007</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>12/31/2009</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Jessica Butler</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr"/>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>01/01/2007</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>12/31/2007</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>David Johnston</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr"/>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>12/31/2009</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Lucie Belanger</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr"/>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr"/>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>12/31/2009</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Hughes Bruyere</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr"/>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr"/>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>12/31/2009</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Elie Zananiri</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr"/>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr"/>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr"/>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>12/31/2007</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Damir Cheremisov</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr"/>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr"/>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>12/31/2006</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Thierry Giles</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr"/>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr"/>
+      <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr"/>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>12/31/2006</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Lysanne Bellemare</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr"/>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Yannick Assogba</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr"/>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Maroussia Lévesque</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr"/>
+      <c r="H480" t="inlineStr"/>
+      <c r="I480" t="inlineStr"/>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Morgan Kennedy</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr"/>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>12/31/2005</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Liu Zehuan</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr"/>
+      <c r="H482" t="inlineStr"/>
+      <c r="I482" t="inlineStr"/>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>12/31/2005</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Hoda Adra</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr"/>
+      <c r="H483" t="inlineStr"/>
+      <c r="I483" t="inlineStr"/>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>12/31/2005</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Elana Rudick</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr"/>
+      <c r="I484" t="inlineStr"/>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>01/01/2004</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>12/31/2004</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Thanh Pham</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr"/>
+      <c r="I485" t="inlineStr"/>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>01/01/2004</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>12/31/2004</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Elio Bidinost</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr"/>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>12/31/2005</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Bruno Nadeau</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr"/>
+      <c r="H487" t="inlineStr"/>
+      <c r="I487" t="inlineStr"/>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>12/31/2005</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>David Bouchard</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr"/>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr"/>
+      <c r="H488" t="inlineStr"/>
+      <c r="I488" t="inlineStr"/>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>12/31/2005</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Frank Tsonis</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr"/>
+      <c r="H489" t="inlineStr"/>
+      <c r="I489" t="inlineStr"/>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>12/31/2003</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Katia Minarikova</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr"/>
+      <c r="H490" t="inlineStr"/>
+      <c r="I490" t="inlineStr"/>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>12/31/2003</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Jonathan Joseph</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr"/>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr"/>
+      <c r="H491" t="inlineStr"/>
+      <c r="I491" t="inlineStr"/>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>12/31/2003</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>David Johnston</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr"/>
+      <c r="H492" t="inlineStr"/>
+      <c r="I492" t="inlineStr"/>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>01/01/2014</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>12/31/2015</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Adriana Navarro Sainz</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr"/>
+      <c r="H493" t="inlineStr"/>
+      <c r="I493" t="inlineStr"/>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>01/01/2014</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>12/31/2015</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Guillaume Bourdon</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr"/>
+      <c r="H494" t="inlineStr"/>
+      <c r="I494" t="inlineStr"/>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>01/01/2012</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>12/31/2013</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Joanna Pederson</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Augmented Reality: Save the Ghost Signs. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr"/>
+      <c r="H495" t="inlineStr"/>
+      <c r="I495" t="inlineStr"/>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>01/01/2010</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>12/31/2011</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Phil Lichti</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>The Soundwalk as Documentary Practice. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr"/>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr"/>
+      <c r="H496" t="inlineStr"/>
+      <c r="I496" t="inlineStr"/>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>01/01/2010</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>12/31/2011</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Santiago Salciado</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Improving the Design Process for Textbooks. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr"/>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr"/>
+      <c r="H497" t="inlineStr"/>
+      <c r="I497" t="inlineStr"/>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>12/31/2007</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Oliver Tsuji</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Narrative in Digital Media. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr"/>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr"/>
+      <c r="H498" t="inlineStr"/>
+      <c r="I498" t="inlineStr"/>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>12/31/2006</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Louis Goupille</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Painterly Approaches to Virtual Environments. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr"/>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr"/>
+      <c r="H499" t="inlineStr"/>
+      <c r="I499" t="inlineStr"/>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>12/31/2006</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Thibaut Duverneix</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr"/>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr"/>
+      <c r="I500" t="inlineStr"/>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>12/31/2004</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Farah Jamaluddin</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr"/>
+      <c r="H501" t="inlineStr"/>
+      <c r="I501" t="inlineStr"/>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>12/31/2005</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Dalia Radwan</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>01/01/2002</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>12/31/2003</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>John Stuart</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr"/>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>01/01/2002</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>12/31/2003</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Justyna Latek</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr"/>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Grad Certificate</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr"/>
+      <c r="H504" t="inlineStr"/>
+      <c r="I504" t="inlineStr"/>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Vanessa Racine</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Anishinaabe Love: Epistemologies &amp; Videogames. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr"/>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr"/>
+      <c r="H505" t="inlineStr"/>
+      <c r="I505" t="inlineStr"/>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>12/31/2025</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Tarcisio Cataldi Tegani (Committee)</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Speculative Vexillology: Exploring National Identity and Imagining Afro-Brazilian Futures through Flags. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr"/>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr"/>
+      <c r="H506" t="inlineStr"/>
+      <c r="I506" t="inlineStr"/>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Caeleigh Lightning Long</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Wawêsiwîn: The Act of Dressing Up — A Research Cree-ation Project. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr"/>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr"/>
+      <c r="H507" t="inlineStr"/>
+      <c r="I507" t="inlineStr"/>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>01/01/2018</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>12/31/2023</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Sébastien Aubin</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Designing Culturally Grounded Cree Syllabaries. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr"/>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr"/>
+      <c r="H508" t="inlineStr"/>
+      <c r="I508" t="inlineStr"/>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>01/01/2018</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>12/31/2021</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Waylon Wilson</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Tuscarora Virtual Realities. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr"/>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr"/>
+      <c r="H509" t="inlineStr"/>
+      <c r="I509" t="inlineStr"/>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>01/01/2017</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>12/31/2019</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Maize Longboat</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Haudenosaunee Storytelling via Video Games. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr"/>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr"/>
+      <c r="H510" t="inlineStr"/>
+      <c r="I510" t="inlineStr"/>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>01/01/2016</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>12/31/2020</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Nicholas Gwyn Shulman (Co-supervisor)</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Network Arts: Seeing and Making Network Organisms. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr"/>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr"/>
+      <c r="H511" t="inlineStr"/>
+      <c r="I511" t="inlineStr"/>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>01/01/2014</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Morgan Kennedy</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Storied Indigeneity in Videogames: Post-Indian Warriors and Indie Japan. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr"/>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr"/>
+      <c r="H512" t="inlineStr"/>
+      <c r="I512" t="inlineStr"/>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>01/01/2012</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>12/31/2015</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Nikolaos Chandolias (Co-supervisor)</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>KinectEcho: Gesture and Vocal Recognition in New Media, Interactive Art and Live Events. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr"/>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr"/>
+      <c r="H513" t="inlineStr"/>
+      <c r="I513" t="inlineStr"/>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>12/31/2007</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Leslie Plumb</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Transversal Entanglements: Research-Creation and the Design Process for Inflexions. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr"/>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr"/>
+      <c r="H514" t="inlineStr"/>
+      <c r="I514" t="inlineStr"/>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>01/01/2004</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Mia Song (Co-supervisor)</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Computer-Assisted Interactive Documentary and Performance Arts in Illimitable Space. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr"/>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr"/>
+      <c r="H515" t="inlineStr"/>
+      <c r="I515" t="inlineStr"/>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>01/01/2003</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>12/31/2005</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Rozita Naghshin (Committee)</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>CASE Tool Simplification Via Task-Sensitive Metaphor. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr"/>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr"/>
+      <c r="H516" t="inlineStr"/>
+      <c r="I516" t="inlineStr"/>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Juliet Mackie</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Reconstituting Indigenous Identities through Portraiture and Storytelling. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr"/>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr"/>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr"/>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Mel Lefebvre</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Healing Through Ancestral Skin Marking: Traditional Tattooing as Healing and (Re)connection for Indigenous People. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr"/>
+      <c r="I518" t="inlineStr"/>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>01/01/2019</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>12/31/2023</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Jessica Barudin (Co-supervisor)</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Re-connecting Through Women's Teachings, Language and Movement. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr"/>
+      <c r="H519" t="inlineStr"/>
+      <c r="I519" t="inlineStr"/>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>01/01/2017</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>12/31/2023</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Suzanne Kite</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Lakota Epistemology, Performance Practice, and Digital Technology. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr"/>
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>01/01/2017</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Nafisa Sarwath (Secondary)</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Indigenous knowledge, resilience and adaptive capacity. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr"/>
+      <c r="H521" t="inlineStr"/>
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>01/01/2016</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>12/31/2021</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Michelle Brown (Secondary)</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>(Re)Coding Resurgence: Indigenous Digital Media Kinnections. University of Hawaii Mānoa.</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr"/>
+      <c r="H522" t="inlineStr"/>
+      <c r="I522" t="inlineStr"/>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>01/01/2007</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>12/31/2014</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Elizabeth LaPensée (Co-supervisor)</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Simon Fraser University.</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr"/>
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>01/01/2008</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>12/31/2012</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Miao Song (Secondary)</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr"/>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>01/01/2008</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>12/31/2011</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>David Johnston (Secondary)</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Aesthetic Animism: Digital Poetry as Ontological Probe. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr"/>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr"/>
+      <c r="H525" t="inlineStr"/>
+      <c r="I525" t="inlineStr"/>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Rozita Naghshin (Committee)</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Software Design as an Aesthetic Design Practice. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr"/>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr"/>
+      <c r="H526" t="inlineStr"/>
+      <c r="I526" t="inlineStr"/>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Melemaikalani Moniz</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow in Abundant Soils. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr"/>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr"/>
+      <c r="H527" t="inlineStr"/>
+      <c r="I527" t="inlineStr"/>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>12/31/2026</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Ceyda Yolgörmez</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Horizon Postdoctoral Fellow in Abundant Intelligences. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr"/>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>01/01/2019</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>12/31/2021</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Leuli Eschraghi</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Horizon Postdoctoral Fellow in Indigenous Futures. Concordia University.</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr"/>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr"/>
+      <c r="H529" t="inlineStr"/>
+      <c r="I529" t="inlineStr"/>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>Supervision</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>01/01/2010</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>12/31/2018</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Acting Chair</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University. Various 1-to-2-week terms.</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr"/>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr"/>
+      <c r="H530" t="inlineStr"/>
+      <c r="I530" t="inlineStr"/>
+      <c r="J530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>09/01/2003</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>08/31/2013</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Computation Arts Undergraduate Program Director / Co-director</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr"/>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="inlineStr"/>
+      <c r="J531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>09/01/2005</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>08/31/2008</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Graduate Program Director</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr"/>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="inlineStr"/>
+      <c r="J532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>09/01/2003</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>08/31/2014</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Computation Lab Director</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr"/>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr"/>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>01/01/2008</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>12/31/2020</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Personnel Committee</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr"/>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr"/>
+      <c r="H534" t="inlineStr"/>
+      <c r="I534" t="inlineStr"/>
+      <c r="J534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>01/01/2002</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>12/31/2014</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>CART Curriculum Committee, Chair</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr"/>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr"/>
+      <c r="J535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>01/01/2002</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Undergraduate and Graduate Admissions Committees</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Department of Design and Computation Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr"/>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr"/>
+      <c r="H536" t="inlineStr"/>
+      <c r="I536" t="inlineStr"/>
+      <c r="J536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Faculty Research Advisory Committee</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Faculty of Fine Arts, Concordia University.</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr"/>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr"/>
+      <c r="H537" t="inlineStr"/>
+      <c r="I537" t="inlineStr"/>
+      <c r="J537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>01/01/2005</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>12/31/2008</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Hexagram-Concordia Steering Committee</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr"/>
+      <c r="I538" t="inlineStr"/>
+      <c r="J538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Co-director, Indigenous Futures Research Center</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr"/>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr"/>
+      <c r="H539" t="inlineStr"/>
+      <c r="I539" t="inlineStr"/>
+      <c r="J539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Indigenous Directions Leadership Council</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr"/>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr"/>
+      <c r="H540" t="inlineStr"/>
+      <c r="I540" t="inlineStr"/>
+      <c r="J540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>01/01/2015</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Milieux Research Institute Advisory Board</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr"/>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr"/>
+      <c r="H541" t="inlineStr"/>
+      <c r="I541" t="inlineStr"/>
+      <c r="J541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>01/01/2015</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>12/31/2018</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Senate Research Committee</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr"/>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr"/>
+      <c r="H542" t="inlineStr"/>
+      <c r="I542" t="inlineStr"/>
+      <c r="J542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>01/01/2009</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>12/31/2018</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Board Member (Founding), Research Centre on Technoculture, Art and Gaming (TAG)</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr"/>
+      <c r="H543" t="inlineStr"/>
+      <c r="I543" t="inlineStr"/>
+      <c r="J543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>01/01/2011</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>12/31/2014</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Faculty Senate</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Concordia University.</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr"/>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr"/>
+      <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr"/>
+      <c r="J544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>12/31/2028</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Advisory Board, Digital Technologies Research Centre</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>National Research Council of Canada.</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr"/>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr"/>
+      <c r="I545" t="inlineStr"/>
+      <c r="J545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>12/31/2023</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Advisory Council on Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Government of Canada.</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr"/>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr"/>
+      <c r="H546" t="inlineStr"/>
+      <c r="I546" t="inlineStr"/>
+      <c r="J546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>12/31/2022</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Canadian Commission for UNESCO Working Groups on AI Ethics &amp; the Sustainable Development Goals</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr"/>
+      <c r="E547" t="inlineStr"/>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr"/>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr"/>
+      <c r="J547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>01/01/2016</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>12/31/2022</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Board Member, imagineNATIVE Film + Media Arts Festival</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr"/>
+      <c r="E548" t="inlineStr"/>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr"/>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr"/>
+      <c r="J548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>01/01/2010</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>12/31/2016</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Founding Member, New Media Advisory Board, imagineNATIVE Film + Media Arts Festival</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr"/>
+      <c r="E549" t="inlineStr"/>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr"/>
+      <c r="H549" t="inlineStr"/>
+      <c r="I549" t="inlineStr"/>
+      <c r="J549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>01/01/2006</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>02/25/2026</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Co-Director, Aboriginal Territories in Cyberspace Research Network</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr"/>
+      <c r="E550" t="inlineStr"/>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr"/>
+      <c r="H550" t="inlineStr"/>
+      <c r="I550" t="inlineStr"/>
+      <c r="J550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>01/01/2013</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>12/31/2016</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>First Peoples Literary Prize Incubating Committee &amp; Founding Advisory Board</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Blue Metropolis International Literary Festival, Montreal, QC.</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr"/>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr"/>
+      <c r="H551" t="inlineStr"/>
+      <c r="I551" t="inlineStr"/>
+      <c r="J551" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/cv-data/cv.xlsx
+++ b/data/cv-data/cv.xlsx
@@ -15447,7 +15447,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15457,18 +15457,18 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Destiny Chescappio</t>
+          <t>Melemaikalani Moniz</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Postdoctoral Fellow in Abundant Soils. Concordia University.</t>
         </is>
       </c>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Postdoc</t>
         </is>
       </c>
       <c r="G407" t="inlineStr"/>
@@ -15488,23 +15488,23 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2026</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Hazel Dreslinski</t>
+          <t>Ceyda Yolgörmez</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Horizon Postdoctoral Fellow in Abundant Intelligences. Concordia University.</t>
         </is>
       </c>
       <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Postdoc</t>
         </is>
       </c>
       <c r="G408" t="inlineStr"/>
@@ -15519,28 +15519,28 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Margaret Summers</t>
+          <t>Leuli Eschraghi</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Horizon Postdoctoral Fellow in Indigenous Futures. Concordia University.</t>
         </is>
       </c>
       <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Postdoc</t>
         </is>
       </c>
       <c r="G409" t="inlineStr"/>
@@ -15555,7 +15555,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15565,18 +15565,18 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Milo Puge</t>
+          <t>Juliet Mackie</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Reconstituting Indigenous Identities through Portraiture and Storytelling. Concordia University.</t>
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G410" t="inlineStr"/>
@@ -15591,28 +15591,28 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>12/31/2025</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Jerwin Cabaneros</t>
+          <t>Mel Lefebvre</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Healing Through Ancestral Skin Marking: Traditional Tattooing as Healing and (Re)connection for Indigenous People. Concordia University.</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G411" t="inlineStr"/>
@@ -15627,28 +15627,28 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2023</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Taylor McArthur</t>
+          <t>Jessica Barudin (Co-supervisor)</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Re-connecting Through Women's Teachings, Language and Movement. Concordia University.</t>
         </is>
       </c>
       <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G412" t="inlineStr"/>
@@ -15663,28 +15663,28 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2023</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Sarah Hontoy-Major</t>
+          <t>Suzanne Kite</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Lakota Epistemology, Performance Practice, and Digital Technology. Concordia University.</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G413" t="inlineStr"/>
@@ -15699,28 +15699,28 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Neko Wong-Houle</t>
+          <t>Nafisa Sarwath (Secondary)</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Indigenous knowledge, resilience and adaptive capacity. Concordia University.</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G414" t="inlineStr"/>
@@ -15735,28 +15735,28 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Ixel Janine</t>
+          <t>Michelle Brown (Secondary)</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>(Re)Coding Resurgence: Indigenous Digital Media Kinnections. University of Hawaii Mānoa.</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G415" t="inlineStr"/>
@@ -15771,28 +15771,28 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2014</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Wan Hua (Wawa) Li</t>
+          <t>Elizabeth LaPensée (Co-supervisor)</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Simon Fraser University.</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G416" t="inlineStr"/>
@@ -15807,28 +15807,28 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2008</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2012</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Bronson Jacque</t>
+          <t>Miao Song (Secondary)</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Concordia University.</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G417" t="inlineStr"/>
@@ -15843,28 +15843,28 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2008</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Shirley Ceravolo</t>
+          <t>David Johnston (Secondary)</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Aesthetic Animism: Digital Poetry as Ontological Probe. Concordia University.</t>
         </is>
       </c>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G418" t="inlineStr"/>
@@ -15879,28 +15879,28 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>12/31/2022</t>
+          <t>12/31/2008</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Alanna Mitchell</t>
+          <t>Rozita Naghshin (Committee)</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Software Design as an Aesthetic Design Practice. Concordia University.</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>PhD</t>
         </is>
       </c>
       <c r="G419" t="inlineStr"/>
@@ -15915,28 +15915,28 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Anthony Lum</t>
+          <t>Vanessa Racine</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Anishinaabe Love: Epistemologies &amp; Videogames. Concordia University.</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G420" t="inlineStr"/>
@@ -15951,28 +15951,28 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>12/31/2022</t>
+          <t>12/31/2025</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Unna Regino</t>
+          <t>Tarcisio Cataldi Tegani (Committee)</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Speculative Vexillology: Exploring National Identity and Imagining Afro-Brazilian Futures through Flags. Concordia University.</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G421" t="inlineStr"/>
@@ -15987,28 +15987,28 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>12/31/2019</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Alaina Perez</t>
+          <t>Caeleigh Lightning Long</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Wawêsiwîn: The Act of Dressing Up — A Research Cree-ation Project. Concordia University.</t>
         </is>
       </c>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G422" t="inlineStr"/>
@@ -16023,28 +16023,28 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>12/31/2020</t>
+          <t>12/31/2023</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Kahentawaks Tiewishaw</t>
+          <t>Sébastien Aubin</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Designing Culturally Grounded Cree Syllabaries. Concordia University.</t>
         </is>
       </c>
       <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G423" t="inlineStr"/>
@@ -16059,28 +16059,28 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>12/31/2019</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Lucas LaRochelle</t>
+          <t>Waylon Wilson</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Tuscarora Virtual Realities. Concordia University.</t>
         </is>
       </c>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G424" t="inlineStr"/>
@@ -16105,18 +16105,18 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Samuelle Bourgault</t>
+          <t>Maize Longboat</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Haudenosaunee Storytelling via Video Games. Concordia University.</t>
         </is>
       </c>
       <c r="E425" t="inlineStr"/>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G425" t="inlineStr"/>
@@ -16131,28 +16131,28 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2020</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Alexandria Alcancia-Shaw</t>
+          <t>Nicholas Gwyn Shulman (Co-supervisor)</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Network Arts: Seeing and Making Network Organisms. Concordia University.</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G426" t="inlineStr"/>
@@ -16167,28 +16167,28 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Asa Perlman</t>
+          <t>Morgan Kennedy</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Storied Indigeneity in Videogames: Post-Indian Warriors and Indie Japan. Concordia University.</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G427" t="inlineStr"/>
@@ -16203,28 +16203,28 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Dion Smith-Dokkie</t>
+          <t>Nikolaos Chandolias (Co-supervisor)</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>KinectEcho: Gesture and Vocal Recognition in New Media, Interactive Art and Live Events. Concordia University.</t>
         </is>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G428" t="inlineStr"/>
@@ -16239,28 +16239,28 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2007</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Eileen Peng</t>
+          <t>Leslie Plumb</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Transversal Entanglements: Research-Creation and the Design Process for Inflexions. Concordia University.</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G429" t="inlineStr"/>
@@ -16275,28 +16275,28 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2004</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2008</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Rudi Aker</t>
+          <t>Mia Song (Co-supervisor)</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Computer-Assisted Interactive Documentary and Performance Arts in Illimitable Space. Concordia University.</t>
         </is>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G430" t="inlineStr"/>
@@ -16311,28 +16311,28 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2005</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Sarah Lauzon</t>
+          <t>Rozita Naghshin (Committee)</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>CASE Tool Simplification Via Task-Sensitive Metaphor. Concordia University.</t>
         </is>
       </c>
       <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Masters</t>
         </is>
       </c>
       <c r="G431" t="inlineStr"/>
@@ -16347,28 +16347,28 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Simon-Albert Boudreault</t>
+          <t>Adriana Navarro Sainz</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G432" t="inlineStr"/>
@@ -16383,28 +16383,28 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Victor Ivanov</t>
+          <t>Guillaume Bourdon</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G433" t="inlineStr"/>
@@ -16419,28 +16419,28 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>12/31/2020</t>
+          <t>12/31/2013</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Emmanuelle Forgues</t>
+          <t>Joanna Pederson</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Augmented Reality: Save the Ghost Signs. Concordia University.</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G434" t="inlineStr"/>
@@ -16455,28 +16455,28 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Roxanne Sirois</t>
+          <t>Phil Lichti</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>The Soundwalk as Documentary Practice. Concordia University.</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G435" t="inlineStr"/>
@@ -16491,28 +16491,28 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Darian Jacobs</t>
+          <t>Santiago Salciado</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Improving the Design Process for Textbooks. Concordia University.</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G436" t="inlineStr"/>
@@ -16527,28 +16527,28 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>12/31/2019</t>
+          <t>12/31/2007</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Travis Mercredi</t>
+          <t>Oliver Tsuji</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Narrative in Digital Media. Concordia University.</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G437" t="inlineStr"/>
@@ -16563,28 +16563,28 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>12/31/2016</t>
+          <t>12/31/2006</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>David Clark</t>
+          <t>Louis Goupille</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Painterly Approaches to Virtual Environments. Concordia University.</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G438" t="inlineStr"/>
@@ -16599,28 +16599,28 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>12/31/2016</t>
+          <t>12/31/2006</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Christina Biron</t>
+          <t>Thibaut Duverneix</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G439" t="inlineStr"/>
@@ -16635,28 +16635,28 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>12/31/2016</t>
+          <t>12/31/2004</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Nicole Linn</t>
+          <t>Farah Jamaluddin</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G440" t="inlineStr"/>
@@ -16671,28 +16671,28 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>12/31/2016</t>
+          <t>12/31/2005</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Mi Lin Li</t>
+          <t>Dalia Radwan</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G441" t="inlineStr"/>
@@ -16707,28 +16707,28 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2002</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2003</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Lianne Maritzer</t>
+          <t>John Stuart</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G442" t="inlineStr"/>
@@ -16743,28 +16743,28 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2002</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>12/31/2018</t>
+          <t>12/31/2003</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Julian Glass-Pilon</t>
+          <t>Justyna Latek</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Undergraduate Research Assistant. Concordia University.</t>
+          <t>Concordia University.</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Grad Certificate</t>
         </is>
       </c>
       <c r="G443" t="inlineStr"/>
@@ -16779,17 +16779,17 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>12/31/2016</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Erica Perrault</t>
+          <t>Destiny Chescappio</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -16815,17 +16815,17 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>12/31/2016</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Charles Hannah</t>
+          <t>Hazel Dreslinski</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -16851,17 +16851,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Nather Aylomen</t>
+          <t>Margaret Summers</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -16887,17 +16887,17 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>01/01/2013</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Näiade Aoun</t>
+          <t>Milo Puge</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -16923,17 +16923,17 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>01/01/2013</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>12/31/2025</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Alicia McDonald-Fortier</t>
+          <t>Jerwin Cabaneros</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -16959,17 +16959,17 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>01/01/2013</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>02/25/2026</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Serge Maheau</t>
+          <t>Taylor McArthur</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -16995,17 +16995,17 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>12/31/2014</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>David Mongeau-Petitepas</t>
+          <t>Sarah Hontoy-Major</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -17031,17 +17031,17 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>12/31/2014</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Saurabh Oberoi</t>
+          <t>Neko Wong-Houle</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -17067,17 +17067,17 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>12/31/2013</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Andy Lunga</t>
+          <t>Ixel Janine</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -17103,17 +17103,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>12/31/2012</t>
+          <t>12/31/2023</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Bronson Zgeb</t>
+          <t>Wan Hua (Wawa) Li</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -17139,17 +17139,17 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>12/31/2012</t>
+          <t>12/31/2023</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Megan Whyte</t>
+          <t>Bronson Jacque</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -17175,17 +17175,17 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2024</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Laura Sirois</t>
+          <t>Shirley Ceravolo</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -17211,17 +17211,17 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2022</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Robert Brais</t>
+          <t>Alanna Mitchell</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -17247,17 +17247,17 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Marie-Joelle Gringas</t>
+          <t>Anthony Lum</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -17283,17 +17283,17 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2022</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Natalie Pan</t>
+          <t>Unna Regino</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -17319,17 +17319,17 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>12/31/2019</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Chris Drogaris</t>
+          <t>Alaina Perez</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -17355,17 +17355,17 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2020</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Tania Alvarez</t>
+          <t>Kahentawaks Tiewishaw</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -17391,17 +17391,17 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>12/31/2010</t>
+          <t>12/31/2019</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Chris Gratton</t>
+          <t>Lucas LaRochelle</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -17427,17 +17427,17 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>12/31/2010</t>
+          <t>12/31/2019</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Brian Li</t>
+          <t>Samuelle Bourgault</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -17463,17 +17463,17 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>12/31/2010</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Charles-Antoine Dupont</t>
+          <t>Alexandria Alcancia-Shaw</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -17499,17 +17499,17 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>12/31/2010</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Ramy Daghistani</t>
+          <t>Asa Perlman</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -17535,17 +17535,17 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>01/01/2009</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>12/31/2013</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Charlotte Fischer</t>
+          <t>Dion Smith-Dokkie</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -17571,17 +17571,17 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>01/01/2009</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>12/31/2013</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Sahar Homami</t>
+          <t>Eileen Peng</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -17607,17 +17607,17 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>12/31/2013</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Nancy Elizabeth-Townsend</t>
+          <t>Rudi Aker</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -17643,17 +17643,17 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Mohannad Al-Khatib</t>
+          <t>Sarah Lauzon</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -17679,17 +17679,17 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>12/31/2009</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Cassandra Lacombe</t>
+          <t>Simon-Albert Boudreault</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -17715,17 +17715,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>12/31/2009</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Raed Mousa</t>
+          <t>Victor Ivanov</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -17751,17 +17751,17 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>12/31/2009</t>
+          <t>12/31/2020</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Jessica Butler</t>
+          <t>Emmanuelle Forgues</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -17787,17 +17787,17 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>12/31/2007</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>David Johnston</t>
+          <t>Roxanne Sirois</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -17823,17 +17823,17 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>12/31/2009</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Lucie Belanger</t>
+          <t>Darian Jacobs</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -17859,17 +17859,17 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>12/31/2009</t>
+          <t>12/31/2019</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Hughes Bruyere</t>
+          <t>Travis Mercredi</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -17895,17 +17895,17 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>12/31/2009</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Elie Zananiri</t>
+          <t>David Clark</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -17931,17 +17931,17 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>12/31/2007</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Damir Cheremisov</t>
+          <t>Christina Biron</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -17967,17 +17967,17 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>12/31/2006</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Thierry Giles</t>
+          <t>Nicole Linn</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -18003,17 +18003,17 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>12/31/2006</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Lysanne Bellemare</t>
+          <t>Mi Lin Li</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -18039,17 +18039,17 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Yannick Assogba</t>
+          <t>Lianne Maritzer</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -18075,17 +18075,17 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>12/31/2018</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Maroussia Lévesque</t>
+          <t>Julian Glass-Pilon</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -18111,17 +18111,17 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Morgan Kennedy</t>
+          <t>Erica Perrault</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -18147,17 +18147,17 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>12/31/2005</t>
+          <t>12/31/2016</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Liu Zehuan</t>
+          <t>Charles Hannah</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -18183,17 +18183,17 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2014</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>12/31/2005</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Hoda Adra</t>
+          <t>Nather Aylomen</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -18219,17 +18219,17 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2013</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>12/31/2005</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Elana Rudick</t>
+          <t>Näiade Aoun</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -18255,17 +18255,17 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>01/01/2004</t>
+          <t>01/01/2013</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>12/31/2004</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Thanh Pham</t>
+          <t>Alicia McDonald-Fortier</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -18291,17 +18291,17 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>01/01/2004</t>
+          <t>01/01/2013</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>12/31/2004</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Elio Bidinost</t>
+          <t>Serge Maheau</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -18327,17 +18327,17 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>12/31/2005</t>
+          <t>12/31/2014</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Bruno Nadeau</t>
+          <t>David Mongeau-Petitepas</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -18363,17 +18363,17 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>12/31/2005</t>
+          <t>12/31/2014</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>David Bouchard</t>
+          <t>Saurabh Oberoi</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -18399,17 +18399,17 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>12/31/2005</t>
+          <t>12/31/2013</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Frank Tsonis</t>
+          <t>Andy Lunga</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -18435,17 +18435,17 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>12/31/2003</t>
+          <t>12/31/2012</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Katia Minarikova</t>
+          <t>Bronson Zgeb</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -18471,17 +18471,17 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>12/31/2003</t>
+          <t>12/31/2012</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Jonathan Joseph</t>
+          <t>Megan Whyte</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -18507,17 +18507,17 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>12/31/2003</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>David Johnston</t>
+          <t>Laura Sirois</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -18543,28 +18543,28 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Adriana Navarro Sainz</t>
+          <t>Robert Brais</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G493" t="inlineStr"/>
@@ -18579,28 +18579,28 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Guillaume Bourdon</t>
+          <t>Marie-Joelle Gringas</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G494" t="inlineStr"/>
@@ -18615,28 +18615,28 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>12/31/2013</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Joanna Pederson</t>
+          <t>Natalie Pan</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Augmented Reality: Save the Ghost Signs. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G495" t="inlineStr"/>
@@ -18656,23 +18656,23 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2015</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Phil Lichti</t>
+          <t>Chris Drogaris</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>The Soundwalk as Documentary Practice. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G496" t="inlineStr"/>
@@ -18697,18 +18697,18 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Santiago Salciado</t>
+          <t>Tania Alvarez</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Improving the Design Process for Textbooks. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G497" t="inlineStr"/>
@@ -18723,28 +18723,28 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>12/31/2007</t>
+          <t>12/31/2010</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Oliver Tsuji</t>
+          <t>Chris Gratton</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Narrative in Digital Media. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G498" t="inlineStr"/>
@@ -18759,28 +18759,28 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>12/31/2006</t>
+          <t>12/31/2010</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Louis Goupille</t>
+          <t>Brian Li</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Painterly Approaches to Virtual Environments. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E499" t="inlineStr"/>
       <c r="F499" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G499" t="inlineStr"/>
@@ -18795,28 +18795,28 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>12/31/2006</t>
+          <t>12/31/2010</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Thibaut Duverneix</t>
+          <t>Charles-Antoine Dupont</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E500" t="inlineStr"/>
       <c r="F500" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G500" t="inlineStr"/>
@@ -18831,28 +18831,28 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>12/31/2004</t>
+          <t>12/31/2010</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Farah Jamaluddin</t>
+          <t>Ramy Daghistani</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G501" t="inlineStr"/>
@@ -18867,28 +18867,28 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2009</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>12/31/2005</t>
+          <t>12/31/2013</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Dalia Radwan</t>
+          <t>Charlotte Fischer</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G502" t="inlineStr"/>
@@ -18903,28 +18903,28 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>01/01/2002</t>
+          <t>01/01/2009</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>12/31/2003</t>
+          <t>12/31/2013</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>John Stuart</t>
+          <t>Sahar Homami</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E503" t="inlineStr"/>
       <c r="F503" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G503" t="inlineStr"/>
@@ -18939,28 +18939,28 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>01/01/2002</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>12/31/2003</t>
+          <t>12/31/2013</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Justyna Latek</t>
+          <t>Nancy Elizabeth-Townsend</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E504" t="inlineStr"/>
       <c r="F504" t="inlineStr">
         <is>
-          <t>Grad Certificate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G504" t="inlineStr"/>
@@ -18975,28 +18975,28 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2011</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Vanessa Racine</t>
+          <t>Mohannad Al-Khatib</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Anishinaabe Love: Epistemologies &amp; Videogames. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E505" t="inlineStr"/>
       <c r="F505" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G505" t="inlineStr"/>
@@ -19011,28 +19011,28 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>12/31/2025</t>
+          <t>12/31/2009</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Tarcisio Cataldi Tegani (Committee)</t>
+          <t>Cassandra Lacombe</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Speculative Vexillology: Exploring National Identity and Imagining Afro-Brazilian Futures through Flags. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E506" t="inlineStr"/>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G506" t="inlineStr"/>
@@ -19047,28 +19047,28 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2009</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Caeleigh Lightning Long</t>
+          <t>Raed Mousa</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Wawêsiwîn: The Act of Dressing Up — A Research Cree-ation Project. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E507" t="inlineStr"/>
       <c r="F507" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G507" t="inlineStr"/>
@@ -19083,28 +19083,28 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2009</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Sébastien Aubin</t>
+          <t>Jessica Butler</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Designing Culturally Grounded Cree Syllabaries. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E508" t="inlineStr"/>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G508" t="inlineStr"/>
@@ -19119,28 +19119,28 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2007</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>12/31/2007</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Waylon Wilson</t>
+          <t>David Johnston</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Tuscarora Virtual Realities. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E509" t="inlineStr"/>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G509" t="inlineStr"/>
@@ -19155,28 +19155,28 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>12/31/2019</t>
+          <t>12/31/2009</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Maize Longboat</t>
+          <t>Lucie Belanger</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Haudenosaunee Storytelling via Video Games. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E510" t="inlineStr"/>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G510" t="inlineStr"/>
@@ -19191,28 +19191,28 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>12/31/2020</t>
+          <t>12/31/2009</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Nicholas Gwyn Shulman (Co-supervisor)</t>
+          <t>Hughes Bruyere</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Network Arts: Seeing and Making Network Organisms. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E511" t="inlineStr"/>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G511" t="inlineStr"/>
@@ -19227,28 +19227,28 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>01/01/2014</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2009</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Morgan Kennedy</t>
+          <t>Elie Zananiri</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Storied Indigeneity in Videogames: Post-Indian Warriors and Indie Japan. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E512" t="inlineStr"/>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G512" t="inlineStr"/>
@@ -19263,28 +19263,28 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>12/31/2015</t>
+          <t>12/31/2007</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Nikolaos Chandolias (Co-supervisor)</t>
+          <t>Damir Cheremisov</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>KinectEcho: Gesture and Vocal Recognition in New Media, Interactive Art and Live Events. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E513" t="inlineStr"/>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G513" t="inlineStr"/>
@@ -19304,23 +19304,23 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>12/31/2007</t>
+          <t>12/31/2006</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Leslie Plumb</t>
+          <t>Thierry Giles</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Transversal Entanglements: Research-Creation and the Design Process for Inflexions. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E514" t="inlineStr"/>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G514" t="inlineStr"/>
@@ -19335,28 +19335,28 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>01/01/2004</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>12/31/2006</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Mia Song (Co-supervisor)</t>
+          <t>Lysanne Bellemare</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Computer-Assisted Interactive Documentary and Performance Arts in Illimitable Space. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E515" t="inlineStr"/>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G515" t="inlineStr"/>
@@ -19371,28 +19371,28 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>01/01/2003</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>12/31/2005</t>
+          <t>12/31/2008</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Rozita Naghshin (Committee)</t>
+          <t>Yannick Assogba</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>CASE Tool Simplification Via Task-Sensitive Metaphor. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E516" t="inlineStr"/>
       <c r="F516" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G516" t="inlineStr"/>
@@ -19407,28 +19407,28 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2008</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Juliet Mackie</t>
+          <t>Maroussia Lévesque</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Reconstituting Indigenous Identities through Portraiture and Storytelling. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E517" t="inlineStr"/>
       <c r="F517" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G517" t="inlineStr"/>
@@ -19443,28 +19443,28 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/31/2008</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Mel Lefebvre</t>
+          <t>Morgan Kennedy</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Healing Through Ancestral Skin Marking: Traditional Tattooing as Healing and (Re)connection for Indigenous People. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E518" t="inlineStr"/>
       <c r="F518" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G518" t="inlineStr"/>
@@ -19479,28 +19479,28 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2005</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Jessica Barudin (Co-supervisor)</t>
+          <t>Liu Zehuan</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Re-connecting Through Women's Teachings, Language and Movement. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E519" t="inlineStr"/>
       <c r="F519" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G519" t="inlineStr"/>
@@ -19515,28 +19515,28 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>12/31/2023</t>
+          <t>12/31/2005</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Suzanne Kite</t>
+          <t>Hoda Adra</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Lakota Epistemology, Performance Practice, and Digital Technology. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E520" t="inlineStr"/>
       <c r="F520" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G520" t="inlineStr"/>
@@ -19551,28 +19551,28 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2005</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Nafisa Sarwath (Secondary)</t>
+          <t>Elana Rudick</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Indigenous knowledge, resilience and adaptive capacity. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G521" t="inlineStr"/>
@@ -19587,28 +19587,28 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2004</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>12/31/2004</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Michelle Brown (Secondary)</t>
+          <t>Thanh Pham</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>(Re)Coding Resurgence: Indigenous Digital Media Kinnections. University of Hawaii Mānoa.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
       <c r="F522" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G522" t="inlineStr"/>
@@ -19623,28 +19623,28 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>01/01/2007</t>
+          <t>01/01/2004</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>12/31/2014</t>
+          <t>12/31/2004</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Elizabeth LaPensée (Co-supervisor)</t>
+          <t>Elio Bidinost</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Simon Fraser University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E523" t="inlineStr"/>
       <c r="F523" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G523" t="inlineStr"/>
@@ -19659,28 +19659,28 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>01/01/2008</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>12/31/2012</t>
+          <t>12/31/2005</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Miao Song (Secondary)</t>
+          <t>Bruno Nadeau</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Experiencing Stories: Narrative and Experience in Interactive Media. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
       <c r="F524" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G524" t="inlineStr"/>
@@ -19695,28 +19695,28 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>01/01/2008</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>12/31/2011</t>
+          <t>12/31/2005</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>David Johnston (Secondary)</t>
+          <t>David Bouchard</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Aesthetic Animism: Digital Poetry as Ontological Probe. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
       <c r="F525" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G525" t="inlineStr"/>
@@ -19731,28 +19731,28 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>12/31/2008</t>
+          <t>12/31/2005</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Rozita Naghshin (Committee)</t>
+          <t>Frank Tsonis</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Software Design as an Aesthetic Design Practice. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E526" t="inlineStr"/>
       <c r="F526" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G526" t="inlineStr"/>
@@ -19767,28 +19767,28 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>02/25/2026</t>
+          <t>12/31/2003</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Melemaikalani Moniz</t>
+          <t>Katia Minarikova</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow in Abundant Soils. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E527" t="inlineStr"/>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G527" t="inlineStr"/>
@@ -19803,28 +19803,28 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>12/31/2026</t>
+          <t>12/31/2003</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Ceyda Yolgörmez</t>
+          <t>Jonathan Joseph</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Horizon Postdoctoral Fellow in Abundant Intelligences. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E528" t="inlineStr"/>
       <c r="F528" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G528" t="inlineStr"/>
@@ -19839,28 +19839,28 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2003</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>12/31/2003</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Leuli Eschraghi</t>
+          <t>David Johnston</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Horizon Postdoctoral Fellow in Indigenous Futures. Concordia University.</t>
+          <t>Undergraduate Research Assistant. Concordia University.</t>
         </is>
       </c>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G529" t="inlineStr"/>
